--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C67:E67</t>
+          <t>C82:E82</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C68:E68</t>
+          <t>C83:E83</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C69:E69</t>
+          <t>C84:E84</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C70:E70</t>
+          <t>C85:E85</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C72:E72</t>
+          <t>C87:E87</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C73:E73</t>
+          <t>C88:E88</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C74:E74</t>
+          <t>C89:E89</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C75:E75</t>
+          <t>C90:E90</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C77:E77</t>
+          <t>C92:E92</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C78:E78</t>
+          <t>C93:E93</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C79:E79</t>
+          <t>C94:E94</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C80:E80</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2706,16 +2706,16 @@
     </row>
     <row r="77">
       <c r="A77" s="10" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
+          <t>Change in Right-of-use Assets</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2024–2026 (3 cells)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>B62:E62</t>
+          <t>C62:E62</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -2736,29 +2736,269 @@
     </row>
     <row r="78">
       <c r="A78" s="10" t="n">
+        <v>113</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Right-of-use Assets Growth</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>C63:E63</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>rou_assets_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n">
+        <v>114</v>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>C64:E64</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n">
+        <v>115</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>C65:E65</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>average_rou_assets, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>B70:E70</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n">
+        <v>117</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>C71:E71</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Change in Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>C72:E72</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n">
+        <v>119</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>C73:E73</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>net_deferred_tax_position</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n">
+        <v>120</v>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>B77:E77</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n">
         <v>121</v>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>PP&amp;E Capex / Revenue</t>
         </is>
       </c>
-      <c r="C78" s="10" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
         <is>
           <t>2023–2026 (4 cells)</t>
         </is>
       </c>
-      <c r="D78" s="10" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>ALT DuPont</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>B63:E63</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>B78:E78</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, revenue_link</t>
         </is>
@@ -6012,7 +6252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -6987,40 +7227,39 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E CAPEX CONTEXT</t>
+          <t>LEASE ROU-ASSET CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Payments for Property, Plant &amp; Equipment (reported)</t>
+          <t>Right-of-use Assets</t>
         </is>
       </c>
       <c r="B61" s="12">
-        <f>'Cash Flow Statement'!B15</f>
+        <f>'Balance Sheet'!B26</f>
         <v/>
       </c>
       <c r="C61" s="12">
-        <f>'Cash Flow Statement'!C15</f>
+        <f>'Balance Sheet'!C26</f>
         <v/>
       </c>
       <c r="D61" s="12">
-        <f>'Cash Flow Statement'!D15</f>
+        <f>'Balance Sheet'!D26</f>
         <v/>
       </c>
       <c r="E61" s="12">
-        <f>'Cash Flow Statement'!E15</f>
+        <f>'Balance Sheet'!E26</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex (−reported)</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="n"/>
+          <t>Change in Right-of-use Assets</t>
+        </is>
+      </c>
       <c r="C62" s="15" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="15" t="n"/>
@@ -7028,111 +7267,111 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PP&amp;E Capex / Revenue</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="n"/>
+          <t>Right-of-use Assets Growth</t>
+        </is>
+      </c>
       <c r="C63" s="14" t="n"/>
       <c r="D63" s="14" t="n"/>
       <c r="E63" s="14" t="n"/>
     </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Average Right-of-use Assets</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="15" t="n"/>
+      <c r="E64" s="15" t="n"/>
+    </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B66" s="12">
-        <f>'Balance Sheet'!B22</f>
-        <v/>
-      </c>
-      <c r="C66" s="12">
-        <f>'Balance Sheet'!C22</f>
-        <v/>
-      </c>
-      <c r="D66" s="12">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
-      </c>
-      <c r="E66" s="12">
-        <f>'Balance Sheet'!E22</f>
-        <v/>
-      </c>
+          <t>Average Right-of-use Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="14" t="n"/>
+      <c r="E65" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="n"/>
-      <c r="D67" s="15" t="n"/>
-      <c r="E67" s="15" t="n"/>
+          <t>DEFERRED-TAX BALANCE CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C68" s="14" t="n"/>
-      <c r="D68" s="14" t="n"/>
-      <c r="E68" s="14" t="n"/>
+          <t>Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="B68" s="12">
+        <f>'Balance Sheet'!B21</f>
+        <v/>
+      </c>
+      <c r="C68" s="12">
+        <f>'Balance Sheet'!C21</f>
+        <v/>
+      </c>
+      <c r="D68" s="12">
+        <f>'Balance Sheet'!D21</f>
+        <v/>
+      </c>
+      <c r="E68" s="12">
+        <f>'Balance Sheet'!E21</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
+          <t>Deferred Tax Liabilities</t>
+        </is>
+      </c>
+      <c r="B69" s="12">
+        <f>'Balance Sheet'!B27</f>
+        <v/>
+      </c>
+      <c r="C69" s="12">
+        <f>'Balance Sheet'!C27</f>
+        <v/>
+      </c>
+      <c r="D69" s="12">
+        <f>'Balance Sheet'!D27</f>
+        <v/>
+      </c>
+      <c r="E69" s="12">
+        <f>'Balance Sheet'!E27</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="n"/>
-      <c r="D70" s="14" t="n"/>
-      <c r="E70" s="14" t="n"/>
+          <t>Net Deferred-Tax Asset Position (DTA − DTL)</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="15" t="n"/>
+      <c r="E70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B71" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C71" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D71" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E71" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
+          <t>Change in Deferred Tax Assets</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="n"/>
+      <c r="D71" s="15" t="n"/>
+      <c r="E71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Deferred Tax Liabilities</t>
         </is>
       </c>
       <c r="C72" s="15" t="n"/>
@@ -7142,62 +7381,50 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="n"/>
-      <c r="D73" s="14" t="n"/>
-      <c r="E73" s="14" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="n"/>
-      <c r="D74" s="15" t="n"/>
-      <c r="E74" s="15" t="n"/>
+          <t>Change in Net Deferred-Tax Asset Position</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="n"/>
-      <c r="D75" s="14" t="n"/>
-      <c r="E75" s="14" t="n"/>
+          <t>PP&amp;E CAPEX CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Payments for Property, Plant &amp; Equipment (reported)</t>
         </is>
       </c>
       <c r="B76" s="12">
-        <f>B66+B71</f>
+        <f>'Cash Flow Statement'!B15</f>
         <v/>
       </c>
       <c r="C76" s="12">
-        <f>C66+C71</f>
+        <f>'Cash Flow Statement'!C15</f>
         <v/>
       </c>
       <c r="D76" s="12">
-        <f>D66+D71</f>
+        <f>'Cash Flow Statement'!D15</f>
         <v/>
       </c>
       <c r="E76" s="12">
-        <f>E66+E71</f>
+        <f>'Cash Flow Statement'!E15</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
+          <t>PP&amp;E Capex (−reported)</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="n"/>
       <c r="C77" s="15" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="15" t="n"/>
@@ -7205,32 +7432,209 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
+          <t>PP&amp;E Capex / Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n"/>
       <c r="C78" s="14" t="n"/>
       <c r="D78" s="14" t="n"/>
       <c r="E78" s="14" t="n"/>
     </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="n"/>
-      <c r="D79" s="15" t="n"/>
-      <c r="E79" s="15" t="n"/>
-    </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B81" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C81" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D81" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E81" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="15" t="n"/>
+      <c r="E82" s="15" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="n"/>
+      <c r="D83" s="14" t="n"/>
+      <c r="E83" s="14" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="n"/>
+      <c r="D84" s="15" t="n"/>
+      <c r="E84" s="15" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="n"/>
+      <c r="D85" s="14" t="n"/>
+      <c r="E85" s="14" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B86" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C86" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D86" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E86" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="n"/>
+      <c r="D87" s="15" t="n"/>
+      <c r="E87" s="15" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="n"/>
+      <c r="D88" s="14" t="n"/>
+      <c r="E88" s="14" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n"/>
+      <c r="D89" s="15" t="n"/>
+      <c r="E89" s="15" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="14" t="n"/>
+      <c r="E90" s="14" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B91" s="12">
+        <f>B81+B86</f>
+        <v/>
+      </c>
+      <c r="C91" s="12">
+        <f>C81+C86</f>
+        <v/>
+      </c>
+      <c r="D91" s="12">
+        <f>D81+D86</f>
+        <v/>
+      </c>
+      <c r="E91" s="12">
+        <f>E81+E86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="15" t="n"/>
+      <c r="E92" s="15" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="n"/>
+      <c r="D93" s="14" t="n"/>
+      <c r="E93" s="14" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="n"/>
+      <c r="D94" s="15" t="n"/>
+      <c r="E94" s="15" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C80" s="14" t="n"/>
-      <c r="D80" s="14" t="n"/>
-      <c r="E80" s="14" t="n"/>
+      <c r="C95" s="14" t="n"/>
+      <c r="D95" s="14" t="n"/>
+      <c r="E95" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C82:E82</t>
+          <t>C87:E87</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C83:E83</t>
+          <t>C88:E88</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C84:E84</t>
+          <t>C89:E89</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C85:E85</t>
+          <t>C90:E90</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C87:E87</t>
+          <t>C92:E92</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C88:E88</t>
+          <t>C93:E93</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C89:E89</t>
+          <t>C94:E94</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C90:E90</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C92:E92</t>
+          <t>C97:E97</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C93:E93</t>
+          <t>C98:E98</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C94:E94</t>
+          <t>C99:E99</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C100:E100</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3001,6 +3001,66 @@
       <c r="F86" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n">
+        <v>124</v>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>B82:E82</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n">
+        <v>125</v>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>B83:E83</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex, revenue_link</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7443,39 +7503,40 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>OPERATING CASH AFTER PP&amp;E CAPEX</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Operating Cash Flow (reported)</t>
         </is>
       </c>
       <c r="B81" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B27</f>
         <v/>
       </c>
       <c r="C81" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C27</f>
         <v/>
       </c>
       <c r="D81" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D27</f>
         <v/>
       </c>
       <c r="E81" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E27</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="B82" s="15" t="n"/>
       <c r="C82" s="15" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="15" t="n"/>
@@ -7483,60 +7544,48 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="n"/>
       <c r="C83" s="14" t="n"/>
       <c r="D83" s="14" t="n"/>
       <c r="E83" s="14" t="n"/>
     </row>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="n"/>
-      <c r="D84" s="15" t="n"/>
-      <c r="E84" s="15" t="n"/>
-    </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="n"/>
-      <c r="D85" s="14" t="n"/>
-      <c r="E85" s="14" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B86" s="12">
-        <f>'Balance Sheet'!B23</f>
+        <f>'Balance Sheet'!B22</f>
         <v/>
       </c>
       <c r="C86" s="12">
-        <f>'Balance Sheet'!C23</f>
+        <f>'Balance Sheet'!C22</f>
         <v/>
       </c>
       <c r="D86" s="12">
-        <f>'Balance Sheet'!D23</f>
+        <f>'Balance Sheet'!D22</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>'Balance Sheet'!E23</f>
+        <f>'Balance Sheet'!E22</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Goodwill</t>
         </is>
       </c>
       <c r="C87" s="15" t="n"/>
@@ -7546,7 +7595,7 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Goodwill Growth</t>
         </is>
       </c>
       <c r="C88" s="14" t="n"/>
@@ -7556,7 +7605,7 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C89" s="15" t="n"/>
@@ -7566,7 +7615,7 @@
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C90" s="14" t="n"/>
@@ -7576,30 +7625,30 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Intangible Assets</t>
         </is>
       </c>
       <c r="B91" s="12">
-        <f>B81+B86</f>
+        <f>'Balance Sheet'!B23</f>
         <v/>
       </c>
       <c r="C91" s="12">
-        <f>C81+C86</f>
+        <f>'Balance Sheet'!C23</f>
         <v/>
       </c>
       <c r="D91" s="12">
-        <f>D81+D86</f>
+        <f>'Balance Sheet'!D23</f>
         <v/>
       </c>
       <c r="E91" s="12">
-        <f>E81+E86</f>
+        <f>'Balance Sheet'!E23</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Change in Intangible Assets</t>
         </is>
       </c>
       <c r="C92" s="15" t="n"/>
@@ -7609,7 +7658,7 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Intangible Assets Growth</t>
         </is>
       </c>
       <c r="C93" s="14" t="n"/>
@@ -7619,7 +7668,7 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C94" s="15" t="n"/>
@@ -7629,12 +7678,75 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C95" s="14" t="n"/>
       <c r="D95" s="14" t="n"/>
       <c r="E95" s="14" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B96" s="12">
+        <f>B86+B91</f>
+        <v/>
+      </c>
+      <c r="C96" s="12">
+        <f>C86+C91</f>
+        <v/>
+      </c>
+      <c r="D96" s="12">
+        <f>D86+D91</f>
+        <v/>
+      </c>
+      <c r="E96" s="12">
+        <f>E86+E91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="n"/>
+      <c r="D97" s="15" t="n"/>
+      <c r="E97" s="15" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="n"/>
+      <c r="D98" s="14" t="n"/>
+      <c r="E98" s="14" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="n"/>
+      <c r="D99" s="15" t="n"/>
+      <c r="E99" s="15" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="n"/>
+      <c r="D100" s="14" t="n"/>
+      <c r="E100" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3061,6 +3061,96 @@
       <c r="F88" s="10" t="inlineStr">
         <is>
           <t>cash_after_ppe_capex, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n">
+        <v>126</v>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>SBC / Revenue</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Earnings Quality</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>B23:E23</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n">
+        <v>127</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>SBC / Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Earnings Quality</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>B24:E24</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>operating_cash_flow_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Reported CFO less SBC add-back</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Earnings Quality</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>B25:E25</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>operating_cash_flow_link</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8239,6 +8329,69 @@
         <f>IF(ABS(E17-((E6-D6)-E15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>STOCK-BASED COMPENSATION CASH DIAGNOSTICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (reported)</t>
+        </is>
+      </c>
+      <c r="B22" s="12">
+        <f>'Cash Flow Statement'!B35</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>'Cash Flow Statement'!C35</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>'Cash Flow Statement'!D35</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>'Cash Flow Statement'!E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>SBC / Revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="14" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="14" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>SBC / Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n"/>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Reported CFO less SBC add-back</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C87:E87</t>
+          <t>C95:E95</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C88:E88</t>
+          <t>C96:E96</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C89:E89</t>
+          <t>C97:E97</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C90:E90</t>
+          <t>C98:E98</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C92:E92</t>
+          <t>C100:E100</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C93:E93</t>
+          <t>C101:E101</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C94:E94</t>
+          <t>C102:E102</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C103:E103</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C97:E97</t>
+          <t>C105:E105</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C98:E98</t>
+          <t>C106:E106</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C99:E99</t>
+          <t>C107:E107</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C100:E100</t>
+          <t>C108:E108</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3151,6 +3151,96 @@
       <c r="F91" s="10" t="inlineStr">
         <is>
           <t>operating_cash_flow_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n">
+        <v>129</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>B87:E87</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>B88:E88</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>acquisition_cash_outflow, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n">
+        <v>131</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>B91:E91</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex, acquisition_cash_outflow</t>
         </is>
       </c>
     </row>
@@ -6402,7 +6492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7645,39 +7735,40 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>ACQUISITION CASH CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Acquisition, net of cash acquired (reported)</t>
         </is>
       </c>
       <c r="B86" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B12</f>
         <v/>
       </c>
       <c r="C86" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C12</f>
         <v/>
       </c>
       <c r="D86" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D12</f>
         <v/>
       </c>
       <c r="E86" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E12</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
+          <t>Acquisition cash outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="n"/>
       <c r="C87" s="15" t="n"/>
       <c r="D87" s="15" t="n"/>
       <c r="E87" s="15" t="n"/>
@@ -7685,123 +7776,86 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Acquisition cash / Revenue</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n"/>
       <c r="C88" s="14" t="n"/>
       <c r="D88" s="14" t="n"/>
       <c r="E88" s="14" t="n"/>
     </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C89" s="15" t="n"/>
-      <c r="D89" s="15" t="n"/>
-      <c r="E89" s="15" t="n"/>
-    </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C90" s="14" t="n"/>
-      <c r="D90" s="14" t="n"/>
-      <c r="E90" s="14" t="n"/>
+          <t>CASH AFTER PP&amp;E CAPEX AND ACQUISITIONS</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B91" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C91" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D91" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E91" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="n"/>
-      <c r="D92" s="15" t="n"/>
-      <c r="E92" s="15" t="n"/>
+          <t>Operating cash after PP&amp;E capex and acquisitions</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="n"/>
-      <c r="D93" s="14" t="n"/>
-      <c r="E93" s="14" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="n"/>
-      <c r="D94" s="15" t="n"/>
-      <c r="E94" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B94" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C94" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D94" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E94" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="n"/>
-      <c r="D95" s="14" t="n"/>
-      <c r="E95" s="14" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="n"/>
+      <c r="D95" s="15" t="n"/>
+      <c r="E95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B96" s="12">
-        <f>B86+B91</f>
-        <v/>
-      </c>
-      <c r="C96" s="12">
-        <f>C86+C91</f>
-        <v/>
-      </c>
-      <c r="D96" s="12">
-        <f>D86+D91</f>
-        <v/>
-      </c>
-      <c r="E96" s="12">
-        <f>E86+E91</f>
-        <v/>
-      </c>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C96" s="14" t="n"/>
+      <c r="D96" s="14" t="n"/>
+      <c r="E96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C97" s="15" t="n"/>
@@ -7811,7 +7865,7 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C98" s="14" t="n"/>
@@ -7821,22 +7875,128 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C99" s="15" t="n"/>
-      <c r="D99" s="15" t="n"/>
-      <c r="E99" s="15" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B99" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C99" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D99" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E99" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="n"/>
+      <c r="D100" s="15" t="n"/>
+      <c r="E100" s="15" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="n"/>
+      <c r="D101" s="14" t="n"/>
+      <c r="E101" s="14" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="n"/>
+      <c r="D102" s="15" t="n"/>
+      <c r="E102" s="15" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="n"/>
+      <c r="D103" s="14" t="n"/>
+      <c r="E103" s="14" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B104" s="12">
+        <f>B94+B99</f>
+        <v/>
+      </c>
+      <c r="C104" s="12">
+        <f>C94+C99</f>
+        <v/>
+      </c>
+      <c r="D104" s="12">
+        <f>D94+D99</f>
+        <v/>
+      </c>
+      <c r="E104" s="12">
+        <f>E94+E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="n"/>
+      <c r="D105" s="15" t="n"/>
+      <c r="E105" s="15" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C106" s="14" t="n"/>
+      <c r="D106" s="14" t="n"/>
+      <c r="E106" s="14" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="n"/>
+      <c r="D107" s="15" t="n"/>
+      <c r="E107" s="15" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C100" s="14" t="n"/>
-      <c r="D100" s="14" t="n"/>
-      <c r="E100" s="14" t="n"/>
+      <c r="C108" s="14" t="n"/>
+      <c r="D108" s="14" t="n"/>
+      <c r="E108" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C95:E95</t>
+          <t>C103:E103</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C96:E96</t>
+          <t>C104:E104</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C97:E97</t>
+          <t>C105:E105</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C98:E98</t>
+          <t>C106:E106</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C100:E100</t>
+          <t>C108:E108</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C101:E101</t>
+          <t>C109:E109</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C102:E102</t>
+          <t>C110:E110</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C103:E103</t>
+          <t>C111:E111</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C105:E105</t>
+          <t>C113:E113</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C106:E106</t>
+          <t>C114:E114</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C107:E107</t>
+          <t>C115:E115</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C108:E108</t>
+          <t>C116:E116</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3241,6 +3241,96 @@
       <c r="F94" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, acquisition_cash_outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n">
+        <v>132</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>B95:E95</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n">
+        <v>133</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>B96:E96</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>share_repurchase_outflow, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>B99:E99</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>ppe_capex, acquisition_cash_outflow, share_repurchase_outflow</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7805,39 +7895,40 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>SHARE REPURCHASE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Repurchase of common stock (reported)</t>
         </is>
       </c>
       <c r="B94" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B10</f>
         <v/>
       </c>
       <c r="C94" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C10</f>
         <v/>
       </c>
       <c r="D94" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D10</f>
         <v/>
       </c>
       <c r="E94" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E10</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
+          <t>Share-repurchase outflow (−reported)</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="n"/>
       <c r="C95" s="15" t="n"/>
       <c r="D95" s="15" t="n"/>
       <c r="E95" s="15" t="n"/>
@@ -7845,123 +7936,86 @@
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Share-repurchase / Revenue</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n"/>
       <c r="C96" s="14" t="n"/>
       <c r="D96" s="14" t="n"/>
       <c r="E96" s="14" t="n"/>
     </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C97" s="15" t="n"/>
-      <c r="D97" s="15" t="n"/>
-      <c r="E97" s="15" t="n"/>
-    </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="n"/>
-      <c r="D98" s="14" t="n"/>
-      <c r="E98" s="14" t="n"/>
+          <t>CASH AFTER PP&amp;E CAPEX, ACQUISITIONS AND REPURCHASES</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B99" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C99" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D99" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E99" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="n"/>
-      <c r="D100" s="15" t="n"/>
-      <c r="E100" s="15" t="n"/>
+          <t>Operating cash after PP&amp;E capex, acquisitions and repurchases</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="15" t="n"/>
+      <c r="D99" s="15" t="n"/>
+      <c r="E99" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="n"/>
-      <c r="D101" s="14" t="n"/>
-      <c r="E101" s="14" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="n"/>
-      <c r="D102" s="15" t="n"/>
-      <c r="E102" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B102" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C102" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D102" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E102" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="n"/>
-      <c r="D103" s="14" t="n"/>
-      <c r="E103" s="14" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="n"/>
+      <c r="D103" s="15" t="n"/>
+      <c r="E103" s="15" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B104" s="12">
-        <f>B94+B99</f>
-        <v/>
-      </c>
-      <c r="C104" s="12">
-        <f>C94+C99</f>
-        <v/>
-      </c>
-      <c r="D104" s="12">
-        <f>D94+D99</f>
-        <v/>
-      </c>
-      <c r="E104" s="12">
-        <f>E94+E99</f>
-        <v/>
-      </c>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C104" s="14" t="n"/>
+      <c r="D104" s="14" t="n"/>
+      <c r="E104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C105" s="15" t="n"/>
@@ -7971,7 +8025,7 @@
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C106" s="14" t="n"/>
@@ -7981,22 +8035,128 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="n"/>
-      <c r="D107" s="15" t="n"/>
-      <c r="E107" s="15" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B107" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C107" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D107" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E107" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="n"/>
+      <c r="D109" s="14" t="n"/>
+      <c r="E109" s="14" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="15" t="n"/>
+      <c r="E110" s="15" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="n"/>
+      <c r="D111" s="14" t="n"/>
+      <c r="E111" s="14" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B112" s="12">
+        <f>B102+B107</f>
+        <v/>
+      </c>
+      <c r="C112" s="12">
+        <f>C102+C107</f>
+        <v/>
+      </c>
+      <c r="D112" s="12">
+        <f>D102+D107</f>
+        <v/>
+      </c>
+      <c r="E112" s="12">
+        <f>E102+E107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="n"/>
+      <c r="D113" s="15" t="n"/>
+      <c r="E113" s="15" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="n"/>
+      <c r="D114" s="14" t="n"/>
+      <c r="E114" s="14" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="n"/>
+      <c r="D115" s="15" t="n"/>
+      <c r="E115" s="15" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C108" s="14" t="n"/>
-      <c r="D108" s="14" t="n"/>
-      <c r="E108" s="14" t="n"/>
+      <c r="C116" s="14" t="n"/>
+      <c r="D116" s="14" t="n"/>
+      <c r="E116" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C103:E103</t>
+          <t>C116:E116</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C104:E104</t>
+          <t>C117:E117</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C105:E105</t>
+          <t>C118:E118</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C106:E106</t>
+          <t>C119:E119</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C108:E108</t>
+          <t>C121:E121</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C109:E109</t>
+          <t>C122:E122</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C110:E110</t>
+          <t>C123:E123</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C111:E111</t>
+          <t>C124:E124</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C113:E113</t>
+          <t>C126:E126</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C114:E114</t>
+          <t>C127:E127</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C115:E115</t>
+          <t>C128:E128</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C116:E116</t>
+          <t>C129:E129</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3331,6 +3331,126 @@
       <c r="F97" s="10" t="inlineStr">
         <is>
           <t>ppe_capex, acquisition_cash_outflow, share_repurchase_outflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>B106:E106</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n">
+        <v>136</v>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>B108:E108</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n">
+        <v>137</v>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>B110:E110</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n">
+        <v>138</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>B112:E112</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
         </is>
       </c>
     </row>
@@ -6582,7 +6702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7965,102 +8085,143 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>CASH ROLL-FORWARD CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Net cash from operating activities (reported)</t>
         </is>
       </c>
       <c r="B102" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Cash Flow Statement'!B27</f>
         <v/>
       </c>
       <c r="C102" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Cash Flow Statement'!C27</f>
         <v/>
       </c>
       <c r="D102" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Cash Flow Statement'!D27</f>
         <v/>
       </c>
       <c r="E102" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Cash Flow Statement'!E27</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C103" s="15" t="n"/>
-      <c r="D103" s="15" t="n"/>
-      <c r="E103" s="15" t="n"/>
+          <t>Net cash from investing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B103" s="12">
+        <f>'Cash Flow Statement'!B13</f>
+        <v/>
+      </c>
+      <c r="C103" s="12">
+        <f>'Cash Flow Statement'!C13</f>
+        <v/>
+      </c>
+      <c r="D103" s="12">
+        <f>'Cash Flow Statement'!D13</f>
+        <v/>
+      </c>
+      <c r="E103" s="12">
+        <f>'Cash Flow Statement'!E13</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C104" s="14" t="n"/>
-      <c r="D104" s="14" t="n"/>
-      <c r="E104" s="14" t="n"/>
+          <t>Net cash from financing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B104" s="12">
+        <f>'Cash Flow Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C104" s="12">
+        <f>'Cash Flow Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D104" s="12">
+        <f>'Cash Flow Statement'!D7</f>
+        <v/>
+      </c>
+      <c r="E104" s="12">
+        <f>'Cash Flow Statement'!E7</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C105" s="15" t="n"/>
-      <c r="D105" s="15" t="n"/>
-      <c r="E105" s="15" t="n"/>
+          <t>Effect of FX on cash (reported)</t>
+        </is>
+      </c>
+      <c r="B105" s="12">
+        <f>'Cash Flow Statement'!B39</f>
+        <v/>
+      </c>
+      <c r="C105" s="12">
+        <f>'Cash Flow Statement'!C39</f>
+        <v/>
+      </c>
+      <c r="D105" s="12">
+        <f>'Cash Flow Statement'!D39</f>
+        <v/>
+      </c>
+      <c r="E105" s="12">
+        <f>'Cash Flow Statement'!E39</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C106" s="14" t="n"/>
-      <c r="D106" s="14" t="n"/>
-      <c r="E106" s="14" t="n"/>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="B106" s="15" t="n"/>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Reported cash change</t>
         </is>
       </c>
       <c r="B107" s="12">
-        <f>'Balance Sheet'!B23</f>
+        <f>'Cash Flow Statement'!B40</f>
         <v/>
       </c>
       <c r="C107" s="12">
-        <f>'Balance Sheet'!C23</f>
+        <f>'Cash Flow Statement'!C40</f>
         <v/>
       </c>
       <c r="D107" s="12">
-        <f>'Balance Sheet'!D23</f>
+        <f>'Cash Flow Statement'!D40</f>
         <v/>
       </c>
       <c r="E107" s="12">
-        <f>'Balance Sheet'!E23</f>
+        <f>'Cash Flow Statement'!E40</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n"/>
       <c r="C108" s="15" t="n"/>
       <c r="D108" s="15" t="n"/>
       <c r="E108" s="15" t="n"/>
@@ -8068,19 +8229,33 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C109" s="14" t="n"/>
-      <c r="D109" s="14" t="n"/>
-      <c r="E109" s="14" t="n"/>
+          <t>Cash beginning (reported)</t>
+        </is>
+      </c>
+      <c r="B109" s="12">
+        <f>'Cash Flow Statement'!B37</f>
+        <v/>
+      </c>
+      <c r="C109" s="12">
+        <f>'Cash Flow Statement'!C37</f>
+        <v/>
+      </c>
+      <c r="D109" s="12">
+        <f>'Cash Flow Statement'!D37</f>
+        <v/>
+      </c>
+      <c r="E109" s="12">
+        <f>'Cash Flow Statement'!E37</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="B110" s="15" t="n"/>
       <c r="C110" s="15" t="n"/>
       <c r="D110" s="15" t="n"/>
       <c r="E110" s="15" t="n"/>
@@ -8088,75 +8263,232 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C111" s="14" t="n"/>
-      <c r="D111" s="14" t="n"/>
-      <c r="E111" s="14" t="n"/>
+          <t>Cash ending (reported)</t>
+        </is>
+      </c>
+      <c r="B111" s="12">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C111" s="12">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D111" s="12">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E111" s="12">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B112" s="12">
-        <f>B102+B107</f>
-        <v/>
-      </c>
-      <c r="C112" s="12">
-        <f>C102+C107</f>
-        <v/>
-      </c>
-      <c r="D112" s="12">
-        <f>D102+D107</f>
-        <v/>
-      </c>
-      <c r="E112" s="12">
-        <f>E102+E107</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C113" s="15" t="n"/>
-      <c r="D113" s="15" t="n"/>
-      <c r="E113" s="15" t="n"/>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="n"/>
+      <c r="C112" s="15" t="n"/>
+      <c r="D112" s="15" t="n"/>
+      <c r="E112" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C114" s="14" t="n"/>
-      <c r="D114" s="14" t="n"/>
-      <c r="E114" s="14" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C115" s="15" t="n"/>
-      <c r="D115" s="15" t="n"/>
-      <c r="E115" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B115" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D115" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E115" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="n"/>
+      <c r="D117" s="14" t="n"/>
+      <c r="E117" s="14" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="n"/>
+      <c r="D119" s="14" t="n"/>
+      <c r="E119" s="14" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B120" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C120" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D120" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E120" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C122" s="14" t="n"/>
+      <c r="D122" s="14" t="n"/>
+      <c r="E122" s="14" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="n"/>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C124" s="14" t="n"/>
+      <c r="D124" s="14" t="n"/>
+      <c r="E124" s="14" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B125" s="12">
+        <f>B115+B120</f>
+        <v/>
+      </c>
+      <c r="C125" s="12">
+        <f>C115+C120</f>
+        <v/>
+      </c>
+      <c r="D125" s="12">
+        <f>D115+D120</f>
+        <v/>
+      </c>
+      <c r="E125" s="12">
+        <f>E115+E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="15" t="n"/>
+      <c r="E126" s="15" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="n"/>
+      <c r="D127" s="14" t="n"/>
+      <c r="E127" s="14" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C116" s="14" t="n"/>
-      <c r="D116" s="14" t="n"/>
-      <c r="E116" s="14" t="n"/>
+      <c r="C129" s="14" t="n"/>
+      <c r="D129" s="14" t="n"/>
+      <c r="E129" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C116:E116</t>
+          <t>C127:E127</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C117:E117</t>
+          <t>C128:E128</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C118:E118</t>
+          <t>C129:E129</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C119:E119</t>
+          <t>C130:E130</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C121:E121</t>
+          <t>C132:E132</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C122:E122</t>
+          <t>C133:E133</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C123:E123</t>
+          <t>C134:E134</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C124:E124</t>
+          <t>C135:E135</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C126:E126</t>
+          <t>C137:E137</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C127:E127</t>
+          <t>C138:E138</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C128:E128</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C129:E129</t>
+          <t>C140:E140</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3451,6 +3451,186 @@
       <c r="F101" s="10" t="inlineStr">
         <is>
           <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>139</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>B118:E118</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>140</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>B119:E119</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>141</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>B120:E120</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>C121:E121</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n">
+        <v>143</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>C122:E122</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n">
+        <v>144</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>C123:E123</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>gross_margin_change, net_operating_expense_burden_change</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8297,69 +8477,97 @@
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>REPORTED MARGIN BRIDGE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Revenue (reported)</t>
         </is>
       </c>
       <c r="B115" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Income Statement'!B19</f>
         <v/>
       </c>
       <c r="C115" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Income Statement'!C19</f>
         <v/>
       </c>
       <c r="D115" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Income Statement'!D19</f>
         <v/>
       </c>
       <c r="E115" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Income Statement'!E19</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="n"/>
-      <c r="D116" s="15" t="n"/>
-      <c r="E116" s="15" t="n"/>
+          <t>Gross profit (reported)</t>
+        </is>
+      </c>
+      <c r="B116" s="12">
+        <f>'Income Statement'!B14</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>'Income Statement'!C14</f>
+        <v/>
+      </c>
+      <c r="D116" s="12">
+        <f>'Income Statement'!D14</f>
+        <v/>
+      </c>
+      <c r="E116" s="12">
+        <f>'Income Statement'!E14</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C117" s="14" t="n"/>
-      <c r="D117" s="14" t="n"/>
-      <c r="E117" s="14" t="n"/>
+          <t>Operating profit (reported)</t>
+        </is>
+      </c>
+      <c r="B117" s="12">
+        <f>'Income Statement'!B16</f>
+        <v/>
+      </c>
+      <c r="C117" s="12">
+        <f>'Income Statement'!C16</f>
+        <v/>
+      </c>
+      <c r="D117" s="12">
+        <f>'Income Statement'!D16</f>
+        <v/>
+      </c>
+      <c r="E117" s="12">
+        <f>'Income Statement'!E16</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n"/>
+      <c r="C118" s="14" t="n"/>
+      <c r="D118" s="14" t="n"/>
+      <c r="E118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="B119" s="14" t="n"/>
       <c r="C119" s="14" t="n"/>
       <c r="D119" s="14" t="n"/>
       <c r="E119" s="14" t="n"/>
@@ -8367,40 +8575,28 @@
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B120" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C120" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D120" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E120" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="B120" s="14" t="n"/>
+      <c r="C120" s="14" t="n"/>
+      <c r="D120" s="14" t="n"/>
+      <c r="E120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="n"/>
-      <c r="D121" s="15" t="n"/>
-      <c r="E121" s="15" t="n"/>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="n"/>
+      <c r="D121" s="14" t="n"/>
+      <c r="E121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Change in net operating expense burden</t>
         </is>
       </c>
       <c r="C122" s="14" t="n"/>
@@ -8410,85 +8606,208 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C123" s="15" t="n"/>
-      <c r="D123" s="15" t="n"/>
-      <c r="E123" s="15" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="10" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C124" s="14" t="n"/>
-      <c r="D124" s="14" t="n"/>
-      <c r="E124" s="14" t="n"/>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="n"/>
+      <c r="D123" s="14" t="n"/>
+      <c r="E123" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B125" s="12">
-        <f>B115+B120</f>
-        <v/>
-      </c>
-      <c r="C125" s="12">
-        <f>C115+C120</f>
-        <v/>
-      </c>
-      <c r="D125" s="12">
-        <f>D115+D120</f>
-        <v/>
-      </c>
-      <c r="E125" s="12">
-        <f>E115+E120</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="n"/>
-      <c r="D126" s="15" t="n"/>
-      <c r="E126" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B126" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C126" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D126" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E126" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="n"/>
-      <c r="D127" s="14" t="n"/>
-      <c r="E127" s="14" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="n"/>
+      <c r="D127" s="15" t="n"/>
+      <c r="E127" s="15" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="n"/>
-      <c r="D128" s="15" t="n"/>
-      <c r="E128" s="15" t="n"/>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C128" s="14" t="n"/>
+      <c r="D128" s="14" t="n"/>
+      <c r="E128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15" t="n"/>
+      <c r="E129" s="15" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C130" s="14" t="n"/>
+      <c r="D130" s="14" t="n"/>
+      <c r="E130" s="14" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B131" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C131" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D131" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E131" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="n"/>
+      <c r="D132" s="15" t="n"/>
+      <c r="E132" s="15" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="n"/>
+      <c r="D133" s="14" t="n"/>
+      <c r="E133" s="14" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="n"/>
+      <c r="D135" s="14" t="n"/>
+      <c r="E135" s="14" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B136" s="12">
+        <f>B126+B131</f>
+        <v/>
+      </c>
+      <c r="C136" s="12">
+        <f>C126+C131</f>
+        <v/>
+      </c>
+      <c r="D136" s="12">
+        <f>D126+D131</f>
+        <v/>
+      </c>
+      <c r="E136" s="12">
+        <f>E126+E131</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="n"/>
+      <c r="D137" s="15" t="n"/>
+      <c r="E137" s="15" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="n"/>
+      <c r="D138" s="14" t="n"/>
+      <c r="E138" s="14" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C129" s="14" t="n"/>
-      <c r="D129" s="14" t="n"/>
-      <c r="E129" s="14" t="n"/>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C127:E127</t>
+          <t>C136:E136</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C128:E128</t>
+          <t>C137:E137</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C129:E129</t>
+          <t>C138:E138</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C130:E130</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C132:E132</t>
+          <t>C141:E141</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C133:E133</t>
+          <t>C142:E142</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C134:E134</t>
+          <t>C143:E143</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C135:E135</t>
+          <t>C144:E144</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C137:E137</t>
+          <t>C146:E146</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C138:E138</t>
+          <t>C147:E147</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C139:E139</t>
+          <t>C148:E148</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C140:E140</t>
+          <t>C149:E149</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3631,6 +3631,156 @@
       <c r="F107" s="10" t="inlineStr">
         <is>
           <t>gross_margin_change, net_operating_expense_burden_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n">
+        <v>145</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>2023–2026 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>B128:E128</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n">
+        <v>146</v>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>C129:E129</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n">
+        <v>147</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>C130:E130</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n">
+        <v>148</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E111" s="10" t="inlineStr">
+        <is>
+          <t>C131:E131</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n">
+        <v>149</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E112" s="10" t="inlineStr">
+        <is>
+          <t>C132:E132</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
         </is>
       </c>
     </row>
@@ -6882,7 +7032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8616,49 +8766,63 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>INVENTORY GROWTH AND INTENSITY CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Inventory (reported)</t>
         </is>
       </c>
       <c r="B126" s="12">
-        <f>'Balance Sheet'!B22</f>
+        <f>'Balance Sheet'!B9</f>
         <v/>
       </c>
       <c r="C126" s="12">
-        <f>'Balance Sheet'!C22</f>
+        <f>'Balance Sheet'!C9</f>
         <v/>
       </c>
       <c r="D126" s="12">
-        <f>'Balance Sheet'!D22</f>
+        <f>'Balance Sheet'!D9</f>
         <v/>
       </c>
       <c r="E126" s="12">
-        <f>'Balance Sheet'!E22</f>
+        <f>'Balance Sheet'!E9</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C127" s="15" t="n"/>
-      <c r="D127" s="15" t="n"/>
-      <c r="E127" s="15" t="n"/>
+          <t>Revenue (reported)</t>
+        </is>
+      </c>
+      <c r="B127" s="12">
+        <f>'Income Statement'!B19</f>
+        <v/>
+      </c>
+      <c r="C127" s="12">
+        <f>'Income Statement'!C19</f>
+        <v/>
+      </c>
+      <c r="D127" s="12">
+        <f>'Income Statement'!D19</f>
+        <v/>
+      </c>
+      <c r="E127" s="12">
+        <f>'Income Statement'!E19</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="B128" s="14" t="n"/>
       <c r="C128" s="14" t="n"/>
       <c r="D128" s="14" t="n"/>
       <c r="E128" s="14" t="n"/>
@@ -8666,7 +8830,7 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
+          <t>Change in inventory</t>
         </is>
       </c>
       <c r="C129" s="15" t="n"/>
@@ -8676,138 +8840,228 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C130" s="14" t="n"/>
-      <c r="D130" s="14" t="n"/>
-      <c r="E130" s="14" t="n"/>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="n"/>
+      <c r="D130" s="15" t="n"/>
+      <c r="E130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B131" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C131" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D131" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E131" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15" t="n"/>
+      <c r="E131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Reconstructed change in inventory</t>
         </is>
       </c>
       <c r="C132" s="15" t="n"/>
       <c r="D132" s="15" t="n"/>
       <c r="E132" s="15" t="n"/>
     </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C133" s="14" t="n"/>
-      <c r="D133" s="14" t="n"/>
-      <c r="E133" s="14" t="n"/>
-    </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="n"/>
-      <c r="D134" s="15" t="n"/>
-      <c r="E134" s="15" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C135" s="14" t="n"/>
-      <c r="D135" s="14" t="n"/>
-      <c r="E135" s="14" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B135" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C135" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D135" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E135" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B136" s="12">
-        <f>B126+B131</f>
-        <v/>
-      </c>
-      <c r="C136" s="12">
-        <f>C126+C131</f>
-        <v/>
-      </c>
-      <c r="D136" s="12">
-        <f>D126+D131</f>
-        <v/>
-      </c>
-      <c r="E136" s="12">
-        <f>E126+E131</f>
-        <v/>
-      </c>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="n"/>
+      <c r="D136" s="15" t="n"/>
+      <c r="E136" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C137" s="15" t="n"/>
-      <c r="D137" s="15" t="n"/>
-      <c r="E137" s="15" t="n"/>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="n"/>
+      <c r="D137" s="14" t="n"/>
+      <c r="E137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C138" s="14" t="n"/>
-      <c r="D138" s="14" t="n"/>
-      <c r="E138" s="14" t="n"/>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C139" s="15" t="n"/>
-      <c r="D139" s="15" t="n"/>
-      <c r="E139" s="15" t="n"/>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="n"/>
+      <c r="D139" s="14" t="n"/>
+      <c r="E139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B140" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C140" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D140" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E140" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C141" s="15" t="n"/>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="n"/>
+      <c r="D142" s="14" t="n"/>
+      <c r="E142" s="14" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C143" s="15" t="n"/>
+      <c r="D143" s="15" t="n"/>
+      <c r="E143" s="15" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="n"/>
+      <c r="D144" s="14" t="n"/>
+      <c r="E144" s="14" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B145" s="12">
+        <f>B135+B140</f>
+        <v/>
+      </c>
+      <c r="C145" s="12">
+        <f>C135+C140</f>
+        <v/>
+      </c>
+      <c r="D145" s="12">
+        <f>D135+D140</f>
+        <v/>
+      </c>
+      <c r="E145" s="12">
+        <f>E135+E140</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="n"/>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="n"/>
+      <c r="D147" s="14" t="n"/>
+      <c r="E147" s="14" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="n"/>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C140" s="14" t="n"/>
-      <c r="D140" s="14" t="n"/>
-      <c r="E140" s="14" t="n"/>
+      <c r="C149" s="14" t="n"/>
+      <c r="D149" s="14" t="n"/>
+      <c r="E149" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C136:E136</t>
+          <t>C139:E139</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C137:E137</t>
+          <t>C140:E140</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C138:E138</t>
+          <t>C141:E141</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C139:E139</t>
+          <t>C142:E142</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C141:E141</t>
+          <t>C144:E144</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C142:E142</t>
+          <t>C145:E145</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C143:E143</t>
+          <t>C146:E146</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C144:E144</t>
+          <t>C147:E147</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C146:E146</t>
+          <t>C149:E149</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C147:E147</t>
+          <t>C150:E150</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C148:E148</t>
+          <t>C151:E151</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C149:E149</t>
+          <t>C152:E152</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -3781,6 +3781,66 @@
       <c r="F112" s="10" t="inlineStr">
         <is>
           <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n">
+        <v>150</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E113" s="10" t="inlineStr">
+        <is>
+          <t>C134:E134</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>2024–2026 (3 cells)</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E114" s="10" t="inlineStr">
+        <is>
+          <t>C135:E135</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8867,103 +8927,103 @@
       <c r="D132" s="15" t="n"/>
       <c r="E132" s="15" t="n"/>
     </row>
+    <row r="133">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>Inventory CF adjustment (reported)</t>
+        </is>
+      </c>
+      <c r="B133" s="12">
+        <f>'Cash Flow Statement'!B25</f>
+        <v/>
+      </c>
+      <c r="C133" s="12">
+        <f>'Cash Flow Statement'!C25</f>
+        <v/>
+      </c>
+      <c r="D133" s="12">
+        <f>'Cash Flow Statement'!D25</f>
+        <v/>
+      </c>
+      <c r="E133" s="12">
+        <f>'Cash Flow Statement'!E25</f>
+        <v/>
+      </c>
+    </row>
     <row r="134">
       <c r="A134" s="10" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
-      </c>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B135" s="12">
-        <f>'Balance Sheet'!B22</f>
-        <v/>
-      </c>
-      <c r="C135" s="12">
-        <f>'Balance Sheet'!C22</f>
-        <v/>
-      </c>
-      <c r="D135" s="12">
-        <f>'Balance Sheet'!D22</f>
-        <v/>
-      </c>
-      <c r="E135" s="12">
-        <f>'Balance Sheet'!E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C136" s="15" t="n"/>
-      <c r="D136" s="15" t="n"/>
-      <c r="E136" s="15" t="n"/>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="n"/>
+      <c r="D135" s="15" t="n"/>
+      <c r="E135" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C137" s="14" t="n"/>
-      <c r="D137" s="14" t="n"/>
-      <c r="E137" s="14" t="n"/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C138" s="15" t="n"/>
-      <c r="D138" s="15" t="n"/>
-      <c r="E138" s="15" t="n"/>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B138" s="12">
+        <f>'Balance Sheet'!B22</f>
+        <v/>
+      </c>
+      <c r="C138" s="12">
+        <f>'Balance Sheet'!C22</f>
+        <v/>
+      </c>
+      <c r="D138" s="12">
+        <f>'Balance Sheet'!D22</f>
+        <v/>
+      </c>
+      <c r="E138" s="12">
+        <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C139" s="14" t="n"/>
-      <c r="D139" s="14" t="n"/>
-      <c r="E139" s="14" t="n"/>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B140" s="12">
-        <f>'Balance Sheet'!B23</f>
-        <v/>
-      </c>
-      <c r="C140" s="12">
-        <f>'Balance Sheet'!C23</f>
-        <v/>
-      </c>
-      <c r="D140" s="12">
-        <f>'Balance Sheet'!D23</f>
-        <v/>
-      </c>
-      <c r="E140" s="12">
-        <f>'Balance Sheet'!E23</f>
-        <v/>
-      </c>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="n"/>
+      <c r="D140" s="14" t="n"/>
+      <c r="E140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C141" s="15" t="n"/>
@@ -8973,7 +9033,7 @@
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C142" s="14" t="n"/>
@@ -8983,50 +9043,50 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C143" s="15" t="n"/>
-      <c r="D143" s="15" t="n"/>
-      <c r="E143" s="15" t="n"/>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B143" s="12">
+        <f>'Balance Sheet'!B23</f>
+        <v/>
+      </c>
+      <c r="C143" s="12">
+        <f>'Balance Sheet'!C23</f>
+        <v/>
+      </c>
+      <c r="D143" s="12">
+        <f>'Balance Sheet'!D23</f>
+        <v/>
+      </c>
+      <c r="E143" s="12">
+        <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="10" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C144" s="14" t="n"/>
-      <c r="D144" s="14" t="n"/>
-      <c r="E144" s="14" t="n"/>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B145" s="12">
-        <f>B135+B140</f>
-        <v/>
-      </c>
-      <c r="C145" s="12">
-        <f>C135+C140</f>
-        <v/>
-      </c>
-      <c r="D145" s="12">
-        <f>D135+D140</f>
-        <v/>
-      </c>
-      <c r="E145" s="12">
-        <f>E135+E140</f>
-        <v/>
-      </c>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="n"/>
+      <c r="D145" s="14" t="n"/>
+      <c r="E145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C146" s="15" t="n"/>
@@ -9036,7 +9096,7 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C147" s="14" t="n"/>
@@ -9046,22 +9106,65 @@
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C148" s="15" t="n"/>
-      <c r="D148" s="15" t="n"/>
-      <c r="E148" s="15" t="n"/>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B148" s="12">
+        <f>B138+B143</f>
+        <v/>
+      </c>
+      <c r="C148" s="12">
+        <f>C138+C143</f>
+        <v/>
+      </c>
+      <c r="D148" s="12">
+        <f>D138+D143</f>
+        <v/>
+      </c>
+      <c r="E148" s="12">
+        <f>E138+E143</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C149" s="15" t="n"/>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="n"/>
+      <c r="D150" s="14" t="n"/>
+      <c r="E150" s="14" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C151" s="15" t="n"/>
+      <c r="D151" s="15" t="n"/>
+      <c r="E151" s="15" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
           <t>Average Goodwill &amp; Intangibles / Revenue</t>
         </is>
       </c>
-      <c r="C149" s="14" t="n"/>
-      <c r="D149" s="14" t="n"/>
-      <c r="E149" s="14" t="n"/>
+      <c r="C152" s="14" t="n"/>
+      <c r="D152" s="14" t="n"/>
+      <c r="E152" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/release/lululemon/Lululemon_Trainer.xlsx
+++ b/release/lululemon/Lululemon_Trainer.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>B34:E34</t>
+          <t>B34:F34</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>B35:E35</t>
+          <t>B35:F35</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>B38:E38</t>
+          <t>B38:F38</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>B44:E44</t>
+          <t>B44:F44</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>B45:E45</t>
+          <t>B45:F45</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>B46:E46</t>
+          <t>B46:F46</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>B47:E47</t>
+          <t>B47:F47</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>B48:E48</t>
+          <t>B48:F48</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>B49:E49</t>
+          <t>B49:F49</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>B50:E50</t>
+          <t>B50:F50</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>B51:E51</t>
+          <t>B51:F51</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>B52:E52</t>
+          <t>B52:F52</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>B53:E53</t>
+          <t>B53:F53</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -945,7 +945,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>B54:E54</t>
+          <t>B54:F54</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>C5:E5</t>
+          <t>C5:F5</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>C10:E10</t>
+          <t>C10:F10</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>C12:E12</t>
+          <t>C12:F12</t>
         </is>
       </c>
       <c r="F21" s="10" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>B5:E5</t>
+          <t>B5:F5</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>B7:E7</t>
+          <t>B7:F7</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>B8:E8</t>
+          <t>B8:F8</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>C11:E11</t>
+          <t>C11:F11</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>C12:E12</t>
+          <t>C12:F12</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>B11:E11</t>
+          <t>B11:F11</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>B12:E12</t>
+          <t>B12:F12</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>B13:E13</t>
+          <t>B13:F13</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>C14:E14</t>
+          <t>C14:F14</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>C15:E15</t>
+          <t>C15:F15</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>C16:E16</t>
+          <t>C16:F16</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>C19:E19</t>
+          <t>C19:F19</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>C20:E20</t>
+          <t>C20:F20</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>C21:E21</t>
+          <t>C21:F21</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>C22:E22</t>
+          <t>C22:F22</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>C23:E23</t>
+          <t>C23:F23</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>C15:E15</t>
+          <t>C15:F15</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>C16:E16</t>
+          <t>C16:F16</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>C17:E17</t>
+          <t>C17:F17</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>2025–2026 (2 cells)</t>
+          <t>2024–2026 (3 cells)</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E41" s="10" t="inlineStr">
         <is>
-          <t>D23:E23</t>
+          <t>D23:F23</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E42" s="10" t="inlineStr">
         <is>
-          <t>C15:E15</t>
+          <t>C15:F15</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="E43" s="10" t="inlineStr">
         <is>
-          <t>C16:E16</t>
+          <t>C16:F16</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="E44" s="10" t="inlineStr">
         <is>
-          <t>C17:E17</t>
+          <t>C17:F17</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>2025–2026 (2 cells)</t>
+          <t>2024–2026 (3 cells)</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>D18:E18</t>
+          <t>D18:F18</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="E46" s="10" t="inlineStr">
         <is>
-          <t>B9:E9</t>
+          <t>B9:F9</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>C12:E12</t>
+          <t>C12:F12</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>C13:E13</t>
+          <t>C13:F13</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>C16:E16</t>
+          <t>C16:F16</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
-          <t>C17:E17</t>
+          <t>C17:F17</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="E51" s="10" t="inlineStr">
         <is>
-          <t>C18:E18</t>
+          <t>C18:F18</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>C19:E19</t>
+          <t>C19:F19</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E53" s="10" t="inlineStr">
         <is>
-          <t>B44:E44</t>
+          <t>B44:F44</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E54" s="10" t="inlineStr">
         <is>
-          <t>B45:E45</t>
+          <t>B45:F45</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
@@ -2065,7 +2065,7 @@
       </c>
       <c r="E55" s="10" t="inlineStr">
         <is>
-          <t>C46:E46</t>
+          <t>C46:F46</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="E56" s="10" t="inlineStr">
         <is>
-          <t>C47:E47</t>
+          <t>C47:F47</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="E57" s="10" t="inlineStr">
         <is>
-          <t>C48:E48</t>
+          <t>C48:F48</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="E58" s="10" t="inlineStr">
         <is>
-          <t>C49:E49</t>
+          <t>C49:F49</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E59" s="10" t="inlineStr">
         <is>
-          <t>B50:E50</t>
+          <t>B50:F50</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>C51:E51</t>
+          <t>C51:F51</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>B55:E55</t>
+          <t>B55:F55</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="E62" s="10" t="inlineStr">
         <is>
-          <t>B56:E56</t>
+          <t>B56:F56</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E63" s="10" t="inlineStr">
         <is>
-          <t>C57:E57</t>
+          <t>C57:F57</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>C58:E58</t>
+          <t>C58:F58</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>C139:E139</t>
+          <t>C139:F139</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>C140:E140</t>
+          <t>C140:F140</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>C141:E141</t>
+          <t>C141:F141</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>C142:E142</t>
+          <t>C142:F142</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>C144:E144</t>
+          <t>C144:F144</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>C145:E145</t>
+          <t>C145:F145</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>C146:E146</t>
+          <t>C146:F146</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>C147:E147</t>
+          <t>C147:F147</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>C149:E149</t>
+          <t>C149:F149</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E74" s="10" t="inlineStr">
         <is>
-          <t>C150:E150</t>
+          <t>C150:F150</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="E75" s="10" t="inlineStr">
         <is>
-          <t>C151:E151</t>
+          <t>C151:F151</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="E76" s="10" t="inlineStr">
         <is>
-          <t>C152:E152</t>
+          <t>C152:F152</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E77" s="10" t="inlineStr">
         <is>
-          <t>C62:E62</t>
+          <t>C62:F62</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>C63:E63</t>
+          <t>C63:F63</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>C64:E64</t>
+          <t>C64:F64</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>C65:E65</t>
+          <t>C65:F65</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>B70:E70</t>
+          <t>B70:F70</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>C71:E71</t>
+          <t>C71:F71</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>C72:E72</t>
+          <t>C72:F72</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>C73:E73</t>
+          <t>C73:F73</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>B77:E77</t>
+          <t>B77:F77</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E86" s="10" t="inlineStr">
         <is>
-          <t>B78:E78</t>
+          <t>B78:F78</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E87" s="10" t="inlineStr">
         <is>
-          <t>B82:E82</t>
+          <t>B82:F82</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>B83:E83</t>
+          <t>B83:F83</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>B23:E23</t>
+          <t>B23:F23</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="E90" s="10" t="inlineStr">
         <is>
-          <t>B24:E24</t>
+          <t>B24:F24</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="E91" s="10" t="inlineStr">
         <is>
-          <t>B25:E25</t>
+          <t>B25:F25</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E92" s="10" t="inlineStr">
         <is>
-          <t>B87:E87</t>
+          <t>B87:F87</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>B88:E88</t>
+          <t>B88:F88</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>B91:E91</t>
+          <t>B91:F91</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>B95:E95</t>
+          <t>B95:F95</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E96" s="10" t="inlineStr">
         <is>
-          <t>B96:E96</t>
+          <t>B96:F96</t>
         </is>
       </c>
       <c r="F96" s="10" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="E97" s="10" t="inlineStr">
         <is>
-          <t>B99:E99</t>
+          <t>B99:F99</t>
         </is>
       </c>
       <c r="F97" s="10" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E98" s="10" t="inlineStr">
         <is>
-          <t>B106:E106</t>
+          <t>B106:F106</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E99" s="10" t="inlineStr">
         <is>
-          <t>B108:E108</t>
+          <t>B108:F108</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="E100" s="10" t="inlineStr">
         <is>
-          <t>B110:E110</t>
+          <t>B110:F110</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E101" s="10" t="inlineStr">
         <is>
-          <t>B112:E112</t>
+          <t>B112:F112</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E102" s="10" t="inlineStr">
         <is>
-          <t>B118:E118</t>
+          <t>B118:F118</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="E103" s="10" t="inlineStr">
         <is>
-          <t>B119:E119</t>
+          <t>B119:F119</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>B120:E120</t>
+          <t>B120:F120</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>C121:E121</t>
+          <t>C121:F121</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E106" s="10" t="inlineStr">
         <is>
-          <t>C122:E122</t>
+          <t>C122:F122</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>C123:E123</t>
+          <t>C123:F123</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>2023–2026 (4 cells)</t>
+          <t>2022–2026 (5 cells)</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>B128:E128</t>
+          <t>B128:F128</t>
         </is>
       </c>
       <c r="F108" s="10" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>C129:E129</t>
+          <t>C129:F129</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="E110" s="10" t="inlineStr">
         <is>
-          <t>C130:E130</t>
+          <t>C130:F130</t>
         </is>
       </c>
       <c r="F110" s="10" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="E111" s="10" t="inlineStr">
         <is>
-          <t>C131:E131</t>
+          <t>C131:F131</t>
         </is>
       </c>
       <c r="F111" s="10" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E112" s="10" t="inlineStr">
         <is>
-          <t>C132:E132</t>
+          <t>C132:F132</t>
         </is>
       </c>
       <c r="F112" s="10" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>C134:E134</t>
+          <t>C134:F134</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>2024–2026 (3 cells)</t>
+          <t>2023–2026 (4 cells)</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>C135:E135</t>
+          <t>C135:F135</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
@@ -3855,7 +3855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3863,6 +3863,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3886,15 +3887,18 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C4" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="D4" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -3920,6 +3924,10 @@
         <f>'Condensed Financials'!E35</f>
         <v/>
       </c>
+      <c r="F5" s="12">
+        <f>'Condensed Financials'!F35</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -3947,6 +3955,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -3955,15 +3968,18 @@
         </is>
       </c>
       <c r="B7" s="18" t="n">
+        <v>130295</v>
+      </c>
+      <c r="C7" s="18" t="n">
         <v>128017</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="D7" s="18" t="n">
         <v>127060</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="E7" s="18" t="n">
         <v>123935</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="F7" s="18" t="n">
         <v>119068</v>
       </c>
     </row>
@@ -3984,6 +4000,7 @@
       <c r="C9" s="19" t="n"/>
       <c r="D9" s="19" t="n"/>
       <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4007,6 +4024,11 @@
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Source unavailable</t>
         </is>
@@ -4026,6 +4048,7 @@
       <c r="C12" s="19" t="n"/>
       <c r="D12" s="19" t="n"/>
       <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -4041,6 +4064,7 @@
       <c r="C13" s="20" t="n"/>
       <c r="D13" s="20" t="n"/>
       <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -4063,6 +4087,7 @@
       <c r="C16" s="15" t="n"/>
       <c r="D16" s="15" t="n"/>
       <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -4078,6 +4103,7 @@
       <c r="C17" s="19" t="n"/>
       <c r="D17" s="19" t="n"/>
       <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -4093,6 +4119,7 @@
       <c r="C18" s="19" t="n"/>
       <c r="D18" s="19" t="n"/>
       <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -4108,6 +4135,7 @@
       <c r="C19" s="19" t="n"/>
       <c r="D19" s="19" t="n"/>
       <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -4130,6 +4158,10 @@
       </c>
       <c r="E20" s="10">
         <f>IF(ABS(E19-E12)&lt;0.0000001,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(ABS(F19-F12)&lt;0.0000001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -4228,7 +4260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4236,6 +4268,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4273,15 +4306,18 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -4292,15 +4328,18 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
+        <v>-28494</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>-65571</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="D7" s="12" t="n">
         <v>-23077</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>-253209</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>253160</v>
       </c>
     </row>
@@ -4311,15 +4350,18 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
+        <v>9732</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>8904</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="D8" s="12" t="n">
         <v>11405</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>93024</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>-59409</v>
       </c>
     </row>
@@ -4330,15 +4372,18 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
+        <v>8782</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>8752</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="D9" s="12" t="n">
         <v>5010</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>2735</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>6961</v>
       </c>
     </row>
@@ -4349,15 +4394,18 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>6.7</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="D10" s="12" t="n">
         <v>12.23</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>14.67</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>13.27</v>
       </c>
     </row>
@@ -4368,15 +4416,18 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
+        <v>956560</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>798133</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="D11" s="12" t="n">
         <v>1538518</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>1654431</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1772934</v>
       </c>
     </row>
@@ -4387,15 +4438,18 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
+        <v>2648052</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>3618178</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="D12" s="12" t="n">
         <v>4009873</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>4317315</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>4818468</v>
       </c>
     </row>
@@ -4406,15 +4460,18 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>6.68</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="D13" s="12" t="n">
         <v>12.2</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>14.64</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>13.26</v>
       </c>
     </row>
@@ -4425,15 +4482,18 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
+        <v>3608565</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <v>4492340</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="D14" s="12" t="n">
         <v>5609405</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>6270811</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>6284132</v>
       </c>
     </row>
@@ -4444,15 +4504,18 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
+        <v>1333869</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>1332571</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="D15" s="12" t="n">
         <v>2175735</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>2576077</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>2238967</v>
       </c>
     </row>
@@ -4463,15 +4526,18 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
+        <v>1333355</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>1328408</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="D16" s="12" t="n">
         <v>2132676</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>2505697</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>2210615</v>
       </c>
     </row>
@@ -4482,15 +4548,18 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
+        <v>358547</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>477771</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="D17" s="12" t="n">
         <v>625545</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>761461</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>659784</v>
       </c>
     </row>
@@ -4501,15 +4570,18 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
+        <v>975322</v>
+      </c>
+      <c r="C18" s="12" t="n">
         <v>854800</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>1550190</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>1814616</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>1579183</v>
       </c>
     </row>
@@ -4520,15 +4592,18 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
+        <v>6256617</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>8110518</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>9619278</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>10588126</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -4539,15 +4614,18 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
+        <v>-18762</v>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>-56667</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="D20" s="12" t="n">
         <v>-11672</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>-160185</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>193751</v>
       </c>
     </row>
@@ -4558,15 +4636,18 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
+        <v>514</v>
+      </c>
+      <c r="C21" s="12" t="n">
         <v>4163</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>43059</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>70380</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>28352</v>
       </c>
     </row>
@@ -4577,15 +4658,18 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
+        <v>2225034</v>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>2757447</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="D22" s="12" t="n">
         <v>3397218</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>3762379</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>4066556</v>
       </c>
     </row>
@@ -4600,7 +4684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4608,6 +4692,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4645,15 +4730,18 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -4664,15 +4752,18 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
+        <v>77001</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>132906</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="D7" s="12" t="n">
         <v>124769</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>120173</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>190657</v>
       </c>
     </row>
@@ -4683,15 +4774,18 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
+        <v>1259871</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <v>1154867</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="D8" s="12" t="n">
         <v>2243971</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>1984336</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -4702,15 +4796,18 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
+        <v>966481</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>1447367</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="D9" s="12" t="n">
         <v>1323602</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>1442081</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>1700753</v>
       </c>
     </row>
@@ -4721,15 +4818,18 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
+        <v>118928</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>185641</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="D10" s="12" t="n">
         <v>183733</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>182253</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>352469</v>
       </c>
     </row>
@@ -4740,15 +4840,18 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
+        <v>192572</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>238672</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="D11" s="12" t="n">
         <v>184502</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>251459</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>211620</v>
       </c>
     </row>
@@ -4759,15 +4862,18 @@
         </is>
       </c>
       <c r="B12" s="12" t="n">
+        <v>2614853</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>3159453</v>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="D12" s="12" t="n">
         <v>4060577</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>3980302</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>4262701</v>
       </c>
     </row>
@@ -4778,15 +4884,18 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
+        <v>289728</v>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>172732</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="D13" s="12" t="n">
         <v>348441</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>271406</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>331421</v>
       </c>
     </row>
@@ -4797,15 +4906,18 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
+        <v>204921</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <v>248167</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="D14" s="12" t="n">
         <v>326110</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>204543</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>187887</v>
       </c>
     </row>
@@ -4816,15 +4928,18 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
+        <v>330800</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>399223</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="D15" s="12" t="n">
         <v>348555</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>559463</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>662982</v>
       </c>
     </row>
@@ -4835,15 +4950,18 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
+        <v>133852</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>174221</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="D16" s="12" t="n">
         <v>12098</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>183126</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>43948</v>
       </c>
     </row>
@@ -4854,15 +4972,18 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
+        <v>188996</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>207972</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="D17" s="12" t="n">
         <v>249270</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>275154</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>298724</v>
       </c>
     </row>
@@ -4873,15 +4994,18 @@
         </is>
       </c>
       <c r="B18" s="12" t="n">
+        <v>48842</v>
+      </c>
+      <c r="C18" s="12" t="n">
         <v>38405</v>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>40308</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>37586</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>45954</v>
       </c>
     </row>
@@ -4892,15 +5016,18 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
+        <v>1405334</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <v>1492198</v>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="D19" s="12" t="n">
         <v>1631261</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>1839630</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>1887548</v>
       </c>
     </row>
@@ -4911,15 +5038,18 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
+        <v>208195</v>
+      </c>
+      <c r="C20" s="12" t="n">
         <v>251478</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="D20" s="12" t="n">
         <v>306479</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>308352</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>316632</v>
       </c>
     </row>
@@ -4930,15 +5060,18 @@
         </is>
       </c>
       <c r="B21" s="12" t="n">
+        <v>6091</v>
+      </c>
+      <c r="C21" s="12" t="n">
         <v>6402</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>9176</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>17085</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>24037</v>
       </c>
     </row>
@@ -4949,15 +5082,18 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
+        <v>386880</v>
+      </c>
+      <c r="C22" s="12" t="n">
         <v>24144</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="D22" s="12" t="n">
         <v>24083</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>159518</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>184911</v>
       </c>
     </row>
@@ -4968,15 +5104,18 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
+        <v>71299</v>
+      </c>
+      <c r="C23" s="12" t="n">
         <v>21961</v>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="D23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>11673</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>6283</v>
       </c>
     </row>
@@ -4987,15 +5126,18 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
+        <v>132102</v>
+      </c>
+      <c r="C24" s="12" t="n">
         <v>156045</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="D24" s="12" t="n">
         <v>186684</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>237841</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>314910</v>
       </c>
     </row>
@@ -5006,15 +5148,18 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
+        <v>927710</v>
+      </c>
+      <c r="C25" s="12" t="n">
         <v>1269614</v>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="D25" s="12" t="n">
         <v>1545811</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>1780617</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>2033720</v>
       </c>
     </row>
@@ -5025,15 +5170,18 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
+        <v>803543</v>
+      </c>
+      <c r="C26" s="12" t="n">
         <v>969419</v>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="D26" s="12" t="n">
         <v>1265610</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>1416256</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>1630181</v>
       </c>
     </row>
@@ -5044,15 +5192,18 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
+        <v>53352</v>
+      </c>
+      <c r="C27" s="12" t="n">
         <v>55084</v>
       </c>
-      <c r="C27" s="12" t="n">
+      <c r="D27" s="12" t="n">
         <v>29522</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>98188</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>52278</v>
       </c>
     </row>
@@ -5063,15 +5214,18 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
+        <v>38074</v>
+      </c>
+      <c r="C28" s="12" t="n">
         <v>28555</v>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="D28" s="12" t="n">
         <v>15864</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -5080,15 +5234,18 @@
         </is>
       </c>
       <c r="B29" s="12" t="n">
+        <v>692056</v>
+      </c>
+      <c r="C29" s="12" t="n">
         <v>862362</v>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="D29" s="12" t="n">
         <v>1154012</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>1300637</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>1499717</v>
       </c>
     </row>
@@ -5099,15 +5256,18 @@
         </is>
       </c>
       <c r="B30" s="12" t="n">
+        <v>13616</v>
+      </c>
+      <c r="C30" s="12" t="n">
         <v>20040</v>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="D30" s="12" t="n">
         <v>29201</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>40790</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>55360</v>
       </c>
     </row>
@@ -5118,15 +5278,18 @@
         </is>
       </c>
       <c r="B31" s="12" t="n">
+        <v>-195917</v>
+      </c>
+      <c r="C31" s="12" t="n">
         <v>-252584</v>
       </c>
-      <c r="C31" s="12" t="n">
+      <c r="D31" s="12" t="n">
         <v>-264256</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>-424441</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>-230690</v>
       </c>
     </row>
@@ -5137,15 +5300,18 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
+        <v>422507</v>
+      </c>
+      <c r="C32" s="12" t="n">
         <v>474645</v>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="D32" s="12" t="n">
         <v>575369</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>638190</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>669392</v>
       </c>
     </row>
@@ -5156,15 +5322,18 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
+        <v>616</v>
+      </c>
+      <c r="C33" s="12" t="n">
         <v>611</v>
       </c>
-      <c r="C33" s="12" t="n">
+      <c r="D33" s="12" t="n">
         <v>606</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="E33" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>557</v>
       </c>
     </row>
@@ -5175,15 +5344,18 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
+        <v>2512840</v>
+      </c>
+      <c r="C34" s="12" t="n">
         <v>2926127</v>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="D34" s="12" t="n">
         <v>3920362</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="E34" s="12" t="n">
         <v>4109717</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>4522581</v>
       </c>
     </row>
@@ -5194,15 +5366,18 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
+        <v>2740046</v>
+      </c>
+      <c r="C35" s="12" t="n">
         <v>3148799</v>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="D35" s="12" t="n">
         <v>4232081</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>4324047</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>4961840</v>
       </c>
     </row>
@@ -5213,15 +5388,18 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
+        <v>4942478</v>
+      </c>
+      <c r="C36" s="12" t="n">
         <v>5607038</v>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="D36" s="12" t="n">
         <v>7091941</v>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="E36" s="12" t="n">
         <v>7603292</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>8456743</v>
       </c>
     </row>
@@ -5232,15 +5410,18 @@
         </is>
       </c>
       <c r="B37" s="12" t="n">
+        <v>4942478</v>
+      </c>
+      <c r="C37" s="12" t="n">
         <v>5607038</v>
       </c>
-      <c r="C37" s="12" t="n">
+      <c r="D37" s="12" t="n">
         <v>7091941</v>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="E37" s="12" t="n">
         <v>7603292</v>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>8456743</v>
       </c>
     </row>
@@ -5251,15 +5432,18 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
+        <v>2202432</v>
+      </c>
+      <c r="C38" s="12" t="n">
         <v>2458239</v>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="D38" s="12" t="n">
         <v>2859860</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="E38" s="12" t="n">
         <v>3279245</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>3494903</v>
       </c>
     </row>
@@ -5274,7 +5458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -5282,6 +5466,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5319,15 +5504,18 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="D6" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="E6" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="F6" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -5338,15 +5526,18 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
+        <v>-844987</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <v>-467487</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="D7" s="12" t="n">
         <v>-548828</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>-1652508</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>-1208656</v>
       </c>
     </row>
@@ -5357,7 +5548,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>-32</v>
+        <v>-770</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>-32</v>
@@ -5366,6 +5557,9 @@
         <v>-32</v>
       </c>
       <c r="E8" s="12" t="n">
+        <v>-32</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <v>-11312</v>
       </c>
     </row>
@@ -5376,15 +5570,18 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
+        <v>18194</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <v>11704</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="D9" s="12" t="n">
         <v>42430</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>19813</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>8377</v>
       </c>
     </row>
@@ -5395,15 +5592,18 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
+        <v>-812602</v>
+      </c>
+      <c r="C10" s="12" t="n">
         <v>-444001</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="D10" s="12" t="n">
         <v>-558652</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>-1636879</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>-1178349</v>
       </c>
     </row>
@@ -5414,15 +5614,18 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
+        <v>-49809</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <v>-35158</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="D11" s="12" t="n">
         <v>-32574</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>-35410</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>-27372</v>
       </c>
     </row>
@@ -5439,9 +5642,12 @@
         <v>0</v>
       </c>
       <c r="D12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>-154146</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5452,15 +5658,18 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
+        <v>-427891</v>
+      </c>
+      <c r="C13" s="12" t="n">
         <v>-569937</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="D13" s="12" t="n">
         <v>-654132</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>-798174</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>-662118</v>
       </c>
     </row>
@@ -5471,15 +5680,18 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <v>20916</v>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="D14" s="12" t="n">
         <v>-658</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>-5009</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>-8521</v>
       </c>
     </row>
@@ -5490,15 +5702,18 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
+        <v>-394502</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <v>-638657</v>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="D15" s="12" t="n">
         <v>-651865</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>-689232</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>-680802</v>
       </c>
     </row>
@@ -5509,15 +5724,18 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
+        <v>-23389</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <v>47804</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="D16" s="12" t="n">
         <v>-1609</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>50213</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>27205</v>
       </c>
     </row>
@@ -5528,383 +5746,443 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
+        <v>117655</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>-107280</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="D17" s="12" t="n">
         <v>177367</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>-57044</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>45856</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Accounts receivable, net</t>
+          <t>Accrued compensation and related expenses</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
-        <v>-58987</v>
+        <v>75273</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>6580</v>
+        <v>47254</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1626</v>
+        <v>70327</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>-65755</v>
+        <v>-112110</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>-24737</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Accrued compensation and related expenses</t>
+          <t>Accrued liabilities and other</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>47254</v>
+        <v>103878</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>70327</v>
+        <v>65364</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>-112110</v>
+        <v>-71734</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>-24737</v>
+        <v>193139</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>98421</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Accrued liabilities and other</t>
+          <t>Current and non-current income taxes payable</t>
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>65364</v>
+        <v>120778</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>-71734</v>
+        <v>35986</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>193139</v>
+        <v>-173196</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>98421</v>
+        <v>157205</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>-150496</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Current and non-current income taxes payable</t>
+          <t>Deferred income taxes</t>
         </is>
       </c>
       <c r="B21" s="12" t="n">
-        <v>35986</v>
+        <v>-5180</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>-173196</v>
+        <v>3042</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>157205</v>
+        <v>-28383</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>-150496</v>
+        <v>57451</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>-53379</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>Deferred income taxes</t>
+          <t>Depreciation and amortization</t>
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>3042</v>
+        <v>224206</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>-28383</v>
+        <v>291791</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>57451</v>
+        <v>379384</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>-53379</v>
+        <v>446524</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>496228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Depreciation and amortization</t>
+          <t>Derecognition of unredeemed gift card liability</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>291791</v>
+        <v>-18699</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>379384</v>
+        <v>-23337</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>446524</v>
+        <v>-28547</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>496228</v>
+        <v>-36231</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>-37766</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Derecognition of unredeemed gift card liability</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>-23337</v>
+        <v>-323609</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>-28547</v>
+        <v>-573438</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>-36231</v>
+        <v>66584</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>-37766</v>
+        <v>-156085</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>-188710</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>lululemon Studio obsolescence provision</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>-573438</v>
+        <v>0</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>66584</v>
+        <v>62928</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>-156085</v>
+        <v>23709</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>-188710</v>
+        <v>0</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>lululemon Studio obsolescence provision</t>
+          <t>Net cash provided by operating activities</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>62928</v>
+        <v>1389108</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>23709</v>
+        <v>966463</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0</v>
+        <v>2296164</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>0</v>
+        <v>2272713</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>1602477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>Net cash provided by operating activities</t>
+          <t>Net income</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>966463</v>
+        <v>975322</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>2296164</v>
+        <v>854800</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>2272713</v>
+        <v>1550190</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1602477</v>
+        <v>1814616</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>1579183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>Net income</t>
+          <t>Other current and non-current liabilities</t>
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>854800</v>
+        <v>30073</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>1550190</v>
+        <v>-2925</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>1814616</v>
+        <v>12230</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>1579183</v>
+        <v>2488</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>20632</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>Other current and non-current liabilities</t>
+          <t>Other non-current assets</t>
         </is>
       </c>
       <c r="B29" s="12" t="n">
-        <v>-2925</v>
+        <v>-17556</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>12230</v>
+        <v>-36518</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2488</v>
+        <v>-53280</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>20632</v>
+        <v>-73205</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>-70351</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>Other non-current assets</t>
+          <t>Prepaid and receivable income taxes</t>
         </is>
       </c>
       <c r="B30" s="12" t="n">
-        <v>-36518</v>
+        <v>20108</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>-53280</v>
+        <v>-66714</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>-73205</v>
+        <v>1908</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>-70351</v>
+        <v>-2031</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>-170216</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>Prepaid and receivable income taxes</t>
+          <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
       <c r="B31" s="12" t="n">
-        <v>-66714</v>
+        <v>-82404</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>1908</v>
+        <v>-54833</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>-2031</v>
+        <v>40587</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>-170216</v>
+        <v>-71789</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>47779</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Prepaid expenses and other current assets</t>
+          <t>Right-of-use lease assets and current and non-current lease liabilities</t>
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>-54833</v>
+        <v>13494</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>40587</v>
+        <v>23905</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>-71789</v>
+        <v>37535</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>47779</v>
+        <v>23501</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>6884</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>Right-of-use lease assets and current and non-current lease liabilities</t>
+          <t>Settlement of derivatives not designated in a hedging relationship</t>
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>23905</v>
+        <v>15191</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>37535</v>
+        <v>-38649</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>23501</v>
+        <v>32527</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>6884</v>
+        <v>-47763</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>-34552</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>Settlement of derivatives not designated in a hedging relationship</t>
+          <t>Stock-based compensation expense</t>
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>-38649</v>
+        <v>69137</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>32527</v>
+        <v>78075</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>-47763</v>
+        <v>93560</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>-34552</v>
+        <v>90011</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>62203</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>Stock-based compensation expense</t>
+          <t>Unredeemed gift card liability</t>
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>78075</v>
+        <v>71441</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>93560</v>
+        <v>68266</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>90011</v>
+        <v>84315</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>62203</v>
+        <v>42410</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>41253</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>Unredeemed gift card liability</t>
+          <t>Cash and cash equivalents, beginning of period</t>
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>68266</v>
+        <v>1150517</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>84315</v>
+        <v>1259871</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>42410</v>
+        <v>1154867</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>41253</v>
+        <v>2243971</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1984336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period</t>
+          <t>Cash and cash equivalents, end of period</t>
         </is>
       </c>
       <c r="B37" s="12" t="n">
@@ -5919,61 +6197,51 @@
       <c r="E37" s="12" t="n">
         <v>1984336</v>
       </c>
+      <c r="F37" s="12" t="n">
+        <v>1807202</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period</t>
+          <t>Effect of foreign currency exchange rate changes on cash and cash equivalents</t>
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>1154867</v>
+        <v>-6876</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>2243971</v>
+        <v>-34043</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>1984336</v>
+        <v>-4100</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>1807202</v>
+        <v>-81666</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>91163</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>Effect of foreign currency exchange rate changes on cash and cash equivalents</t>
+          <t>Increase (decrease) in cash and cash equivalents</t>
         </is>
       </c>
       <c r="B39" s="12" t="n">
-        <v>-34043</v>
+        <v>109354</v>
       </c>
       <c r="C39" s="12" t="n">
-        <v>-4100</v>
+        <v>-105004</v>
       </c>
       <c r="D39" s="12" t="n">
-        <v>-81666</v>
+        <v>1089104</v>
       </c>
       <c r="E39" s="12" t="n">
-        <v>91163</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>Increase (decrease) in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n">
-        <v>-105004</v>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>1089104</v>
-      </c>
-      <c r="D40" s="12" t="n">
         <v>-259635</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>-177134</v>
       </c>
     </row>
@@ -5988,7 +6256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5997,7 +6265,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6026,18 +6295,21 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="D5" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="E5" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="F5" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="G5" s="11" t="n">
         <v>46054</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -6055,15 +6327,18 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
+        <v>77001</v>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>132906</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>124769</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>120173</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="G6" s="12" t="n">
         <v>190657</v>
       </c>
     </row>
@@ -6079,15 +6354,18 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
+        <v>1259871</v>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>1154867</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>2243971</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>1984336</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="G7" s="12" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -6103,15 +6381,18 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
+        <v>966481</v>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>1447367</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>1323602</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>1442081</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="G8" s="12" t="n">
         <v>1700753</v>
       </c>
     </row>
@@ -6127,15 +6408,18 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
+        <v>118928</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>185641</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>183733</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>182253</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="G9" s="12" t="n">
         <v>352469</v>
       </c>
     </row>
@@ -6151,15 +6435,18 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
+        <v>192572</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>238672</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>184502</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>251459</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="G10" s="12" t="n">
         <v>211620</v>
       </c>
     </row>
@@ -6175,15 +6462,18 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
+        <v>289728</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>172732</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>348441</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>271406</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>331421</v>
       </c>
     </row>
@@ -6199,15 +6489,18 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
+        <v>204921</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>248167</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>326110</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>204543</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>187887</v>
       </c>
     </row>
@@ -6223,15 +6516,18 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
+        <v>330800</v>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>399223</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>348555</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>559463</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>662982</v>
       </c>
     </row>
@@ -6247,15 +6543,18 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
+        <v>133852</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>174221</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>12098</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>183126</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>43948</v>
       </c>
     </row>
@@ -6270,18 +6569,21 @@
         <v/>
       </c>
       <c r="C15" s="12" t="n">
+        <v>188996</v>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>207972</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>249270</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>275154</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>298724</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Lease liability concept — operating vs financial judgment</t>
         </is>
@@ -6298,18 +6600,21 @@
         <v/>
       </c>
       <c r="C16" s="12" t="n">
+        <v>48842</v>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>38405</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>40308</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>37586</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>45954</v>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Explicit residual balance-sheet concept identifies side/horizon but not economic nature — operating vs financial judgment</t>
         </is>
@@ -6327,15 +6632,18 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
+        <v>208195</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>251478</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>306479</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>308352</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>316632</v>
       </c>
     </row>
@@ -6351,18 +6659,21 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
+        <v>6091</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>6402</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>9176</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>17085</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>24037</v>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Deferred tax asset concept — operating vs exclude judgment</t>
         </is>
@@ -6380,15 +6691,18 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
+        <v>386880</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>24144</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>24083</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>159518</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>184911</v>
       </c>
     </row>
@@ -6404,15 +6718,18 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
+        <v>71299</v>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>21961</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>11673</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>6283</v>
       </c>
     </row>
@@ -6427,18 +6744,21 @@
         <v/>
       </c>
       <c r="C21" s="12" t="n">
+        <v>132102</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>156045</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>186684</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>237841</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>314910</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Explicit residual balance-sheet concept identifies side/horizon but not economic nature — operating vs financial judgment</t>
         </is>
@@ -6456,15 +6776,18 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
+        <v>927710</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>1269614</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>1545811</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>1780617</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>2033720</v>
       </c>
     </row>
@@ -6480,18 +6803,21 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
+        <v>803543</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>969419</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>1265610</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>1416256</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>1630181</v>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Lease/ROU asset concept — operating vs financial judgment</t>
         </is>
@@ -6509,18 +6835,21 @@
         </is>
       </c>
       <c r="C24" s="12" t="n">
+        <v>53352</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>55084</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>29522</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>98188</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>52278</v>
       </c>
-      <c r="G24" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Deferred tax liability concept — operating vs exclude judgment</t>
         </is>
@@ -6538,15 +6867,18 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
+        <v>38074</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>28555</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>15864</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -6559,18 +6891,21 @@
         <v/>
       </c>
       <c r="C26" s="12" t="n">
+        <v>692056</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>862362</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>1154012</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>1300637</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>1499717</v>
       </c>
-      <c r="G26" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Lease liability concept — operating vs financial judgment</t>
         </is>
@@ -6587,18 +6922,21 @@
         <v/>
       </c>
       <c r="C27" s="12" t="n">
+        <v>13616</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>20040</v>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="E27" s="12" t="n">
         <v>29201</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>40790</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>55360</v>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>⚠ Review: Explicit residual balance-sheet concept identifies side/horizon but not economic nature — operating vs financial judgment</t>
         </is>
@@ -6616,15 +6954,18 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
+        <v>-195917</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>-252584</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>-264256</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>-424441</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>-230690</v>
       </c>
     </row>
@@ -6640,15 +6981,18 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
+        <v>422507</v>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>474645</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>575369</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>638190</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>669392</v>
       </c>
     </row>
@@ -6664,15 +7008,18 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
+        <v>616</v>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>611</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>606</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>581</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>557</v>
       </c>
     </row>
@@ -6688,15 +7035,18 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
+        <v>2512840</v>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>2926127</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="E31" s="12" t="n">
         <v>3920362</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>4109717</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>4522581</v>
       </c>
     </row>
@@ -6707,15 +7057,18 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C33" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="D33" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="E33" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="F33" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -6729,6 +7082,7 @@
       <c r="C34" s="13" t="n"/>
       <c r="D34" s="13" t="n"/>
       <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
@@ -6740,6 +7094,7 @@
       <c r="C35" s="13" t="n"/>
       <c r="D35" s="13" t="n"/>
       <c r="E35" s="13" t="n"/>
+      <c r="F35" s="13" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -6763,6 +7118,10 @@
         <f>'Income Statement'!E15</f>
         <v/>
       </c>
+      <c r="F36" s="10">
+        <f>'Income Statement'!F15</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -6784,6 +7143,10 @@
       </c>
       <c r="E37" s="10">
         <f>'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>'Income Statement'!F17</f>
         <v/>
       </c>
     </row>
@@ -6797,6 +7160,7 @@
       <c r="C38" s="14" t="n"/>
       <c r="D38" s="14" t="n"/>
       <c r="E38" s="14" t="n"/>
+      <c r="F38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -6824,6 +7188,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -6851,6 +7220,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -6874,6 +7248,11 @@
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Source unavailable</t>
         </is>
@@ -6896,6 +7275,7 @@
       <c r="C44" s="15" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -6907,6 +7287,7 @@
       <c r="C45" s="15" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -6918,6 +7299,7 @@
       <c r="C46" s="15" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -6929,6 +7311,7 @@
       <c r="C47" s="15" t="n"/>
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -6940,6 +7323,7 @@
       <c r="C48" s="15" t="n"/>
       <c r="D48" s="15" t="n"/>
       <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -6951,6 +7335,7 @@
       <c r="C49" s="15" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -6962,6 +7347,7 @@
       <c r="C50" s="15" t="n"/>
       <c r="D50" s="15" t="n"/>
       <c r="E50" s="15" t="n"/>
+      <c r="F50" s="15" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -6973,6 +7359,7 @@
       <c r="C51" s="15" t="n"/>
       <c r="D51" s="15" t="n"/>
       <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -6984,6 +7371,7 @@
       <c r="C52" s="15" t="n"/>
       <c r="D52" s="15" t="n"/>
       <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
@@ -6995,6 +7383,7 @@
       <c r="C53" s="15" t="n"/>
       <c r="D53" s="15" t="n"/>
       <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
@@ -7006,6 +7395,7 @@
       <c r="C54" s="15" t="n"/>
       <c r="D54" s="15" t="n"/>
       <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
@@ -7029,6 +7419,10 @@
         <f>'Balance Sheet'!E35</f>
         <v/>
       </c>
+      <c r="F55" s="12">
+        <f>'Balance Sheet'!F35</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -7052,6 +7446,10 @@
         <f>E53+E54</f>
         <v/>
       </c>
+      <c r="F56" s="12">
+        <f>F53+F54</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -7073,6 +7471,10 @@
       </c>
       <c r="E57" s="10">
         <f>IF(ABS(E54-E55)&lt;1,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="F57" s="10">
+        <f>IF(ABS(F54-F55)&lt;1,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -7092,7 +7494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7100,6 +7502,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7123,15 +7526,18 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C4" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="D4" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -7149,6 +7555,7 @@
       <c r="C5" s="14" t="n"/>
       <c r="D5" s="14" t="n"/>
       <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -7176,6 +7583,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -7203,6 +7615,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -7230,6 +7647,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -7253,6 +7675,11 @@
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Source unavailable</t>
         </is>
@@ -7272,6 +7699,7 @@
       <c r="C10" s="13" t="n"/>
       <c r="D10" s="13" t="n"/>
       <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -7295,6 +7723,11 @@
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Source unavailable</t>
         </is>
@@ -7314,6 +7747,7 @@
       <c r="C12" s="14" t="n"/>
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -7336,6 +7770,7 @@
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -7351,6 +7786,7 @@
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -7366,6 +7802,7 @@
       <c r="C17" s="16" t="n"/>
       <c r="D17" s="16" t="n"/>
       <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -7393,6 +7830,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -7420,6 +7862,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7454,6 +7901,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -7473,6 +7925,7 @@
       </c>
       <c r="D23" s="16" t="n"/>
       <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -7500,6 +7953,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -7527,6 +7985,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
@@ -7554,6 +8017,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -7581,6 +8049,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -7608,6 +8081,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
@@ -7642,6 +8120,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
@@ -7669,6 +8152,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
@@ -7703,6 +8191,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
@@ -7730,6 +8223,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
@@ -7757,6 +8255,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
@@ -7784,6 +8287,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
@@ -7811,6 +8319,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
@@ -7838,6 +8351,11 @@
           <t>Source unavailable</t>
         </is>
       </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
@@ -7861,6 +8379,11 @@
         </is>
       </c>
       <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Source unavailable</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>Source unavailable</t>
         </is>
@@ -7883,6 +8406,7 @@
       <c r="C44" s="15" t="n"/>
       <c r="D44" s="15" t="n"/>
       <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
@@ -7894,6 +8418,7 @@
       <c r="C45" s="15" t="n"/>
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
@@ -7909,6 +8434,7 @@
       <c r="C46" s="15" t="n"/>
       <c r="D46" s="15" t="n"/>
       <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
@@ -7924,6 +8450,7 @@
       <c r="C47" s="16" t="n"/>
       <c r="D47" s="16" t="n"/>
       <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
@@ -7939,6 +8466,7 @@
       <c r="C48" s="14" t="n"/>
       <c r="D48" s="14" t="n"/>
       <c r="E48" s="14" t="n"/>
+      <c r="F48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
@@ -7954,6 +8482,7 @@
       <c r="C49" s="15" t="n"/>
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
@@ -7965,6 +8494,7 @@
       <c r="C50" s="14" t="n"/>
       <c r="D50" s="14" t="n"/>
       <c r="E50" s="14" t="n"/>
+      <c r="F50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
@@ -7980,6 +8510,7 @@
       <c r="C51" s="14" t="n"/>
       <c r="D51" s="14" t="n"/>
       <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
@@ -8002,6 +8533,10 @@
       </c>
       <c r="E52" s="10">
         <f>IF(OR(ISNA(E47),ISNA(E48)),"N/A",IF(ABS(E47*E48-1)&lt;0.0000001,"OK","CHECK"))</f>
+        <v/>
+      </c>
+      <c r="F52" s="10">
+        <f>IF(OR(ISNA(F47),ISNA(F48)),"N/A",IF(ABS(F47*F48-1)&lt;0.0000001,"OK","CHECK"))</f>
         <v/>
       </c>
     </row>
@@ -8022,6 +8557,7 @@
       <c r="C55" s="15" t="n"/>
       <c r="D55" s="15" t="n"/>
       <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
@@ -8033,6 +8569,7 @@
       <c r="C56" s="14" t="n"/>
       <c r="D56" s="14" t="n"/>
       <c r="E56" s="14" t="n"/>
+      <c r="F56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
@@ -8048,6 +8585,7 @@
       <c r="C57" s="15" t="n"/>
       <c r="D57" s="15" t="n"/>
       <c r="E57" s="15" t="n"/>
+      <c r="F57" s="15" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
@@ -8063,6 +8601,7 @@
       <c r="C58" s="14" t="n"/>
       <c r="D58" s="14" t="n"/>
       <c r="E58" s="14" t="n"/>
+      <c r="F58" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
@@ -8091,6 +8630,10 @@
       </c>
       <c r="E61" s="12">
         <f>'Balance Sheet'!E26</f>
+        <v/>
+      </c>
+      <c r="F61" s="12">
+        <f>'Balance Sheet'!F26</f>
         <v/>
       </c>
     </row>
@@ -8103,6 +8646,7 @@
       <c r="C62" s="15" t="n"/>
       <c r="D62" s="15" t="n"/>
       <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
@@ -8113,6 +8657,7 @@
       <c r="C63" s="14" t="n"/>
       <c r="D63" s="14" t="n"/>
       <c r="E63" s="14" t="n"/>
+      <c r="F63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
@@ -8123,6 +8668,7 @@
       <c r="C64" s="15" t="n"/>
       <c r="D64" s="15" t="n"/>
       <c r="E64" s="15" t="n"/>
+      <c r="F64" s="15" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
@@ -8133,6 +8679,7 @@
       <c r="C65" s="14" t="n"/>
       <c r="D65" s="14" t="n"/>
       <c r="E65" s="14" t="n"/>
+      <c r="F65" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
@@ -8163,6 +8710,10 @@
         <f>'Balance Sheet'!E21</f>
         <v/>
       </c>
+      <c r="F68" s="12">
+        <f>'Balance Sheet'!F21</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
@@ -8184,6 +8735,10 @@
       </c>
       <c r="E69" s="12">
         <f>'Balance Sheet'!E27</f>
+        <v/>
+      </c>
+      <c r="F69" s="12">
+        <f>'Balance Sheet'!F27</f>
         <v/>
       </c>
     </row>
@@ -8197,6 +8752,7 @@
       <c r="C70" s="15" t="n"/>
       <c r="D70" s="15" t="n"/>
       <c r="E70" s="15" t="n"/>
+      <c r="F70" s="15" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
@@ -8207,6 +8763,7 @@
       <c r="C71" s="15" t="n"/>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="15" t="n"/>
+      <c r="F71" s="15" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
@@ -8217,6 +8774,7 @@
       <c r="C72" s="15" t="n"/>
       <c r="D72" s="15" t="n"/>
       <c r="E72" s="15" t="n"/>
+      <c r="F72" s="15" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
@@ -8227,6 +8785,7 @@
       <c r="C73" s="15" t="n"/>
       <c r="D73" s="15" t="n"/>
       <c r="E73" s="15" t="n"/>
+      <c r="F73" s="15" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
@@ -8255,6 +8814,10 @@
       </c>
       <c r="E76" s="12">
         <f>'Cash Flow Statement'!E15</f>
+        <v/>
+      </c>
+      <c r="F76" s="12">
+        <f>'Cash Flow Statement'!F15</f>
         <v/>
       </c>
     </row>
@@ -8268,6 +8831,7 @@
       <c r="C77" s="15" t="n"/>
       <c r="D77" s="15" t="n"/>
       <c r="E77" s="15" t="n"/>
+      <c r="F77" s="15" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
@@ -8279,6 +8843,7 @@
       <c r="C78" s="14" t="n"/>
       <c r="D78" s="14" t="n"/>
       <c r="E78" s="14" t="n"/>
+      <c r="F78" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
@@ -8294,19 +8859,23 @@
         </is>
       </c>
       <c r="B81" s="12">
-        <f>'Cash Flow Statement'!B27</f>
+        <f>'Cash Flow Statement'!B26</f>
         <v/>
       </c>
       <c r="C81" s="12">
-        <f>'Cash Flow Statement'!C27</f>
+        <f>'Cash Flow Statement'!C26</f>
         <v/>
       </c>
       <c r="D81" s="12">
-        <f>'Cash Flow Statement'!D27</f>
+        <f>'Cash Flow Statement'!D26</f>
         <v/>
       </c>
       <c r="E81" s="12">
-        <f>'Cash Flow Statement'!E27</f>
+        <f>'Cash Flow Statement'!E26</f>
+        <v/>
+      </c>
+      <c r="F81" s="12">
+        <f>'Cash Flow Statement'!F26</f>
         <v/>
       </c>
     </row>
@@ -8320,6 +8889,7 @@
       <c r="C82" s="15" t="n"/>
       <c r="D82" s="15" t="n"/>
       <c r="E82" s="15" t="n"/>
+      <c r="F82" s="15" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
@@ -8331,6 +8901,7 @@
       <c r="C83" s="14" t="n"/>
       <c r="D83" s="14" t="n"/>
       <c r="E83" s="14" t="n"/>
+      <c r="F83" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
@@ -8359,6 +8930,10 @@
       </c>
       <c r="E86" s="12">
         <f>'Cash Flow Statement'!E12</f>
+        <v/>
+      </c>
+      <c r="F86" s="12">
+        <f>'Cash Flow Statement'!F12</f>
         <v/>
       </c>
     </row>
@@ -8372,6 +8947,7 @@
       <c r="C87" s="15" t="n"/>
       <c r="D87" s="15" t="n"/>
       <c r="E87" s="15" t="n"/>
+      <c r="F87" s="15" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
@@ -8383,6 +8959,7 @@
       <c r="C88" s="14" t="n"/>
       <c r="D88" s="14" t="n"/>
       <c r="E88" s="14" t="n"/>
+      <c r="F88" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
@@ -8401,6 +8978,7 @@
       <c r="C91" s="15" t="n"/>
       <c r="D91" s="15" t="n"/>
       <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
@@ -8429,6 +9007,10 @@
       </c>
       <c r="E94" s="12">
         <f>'Cash Flow Statement'!E10</f>
+        <v/>
+      </c>
+      <c r="F94" s="12">
+        <f>'Cash Flow Statement'!F10</f>
         <v/>
       </c>
     </row>
@@ -8442,6 +9024,7 @@
       <c r="C95" s="15" t="n"/>
       <c r="D95" s="15" t="n"/>
       <c r="E95" s="15" t="n"/>
+      <c r="F95" s="15" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
@@ -8453,6 +9036,7 @@
       <c r="C96" s="14" t="n"/>
       <c r="D96" s="14" t="n"/>
       <c r="E96" s="14" t="n"/>
+      <c r="F96" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
@@ -8471,6 +9055,7 @@
       <c r="C99" s="15" t="n"/>
       <c r="D99" s="15" t="n"/>
       <c r="E99" s="15" t="n"/>
+      <c r="F99" s="15" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
@@ -8486,19 +9071,23 @@
         </is>
       </c>
       <c r="B102" s="12">
-        <f>'Cash Flow Statement'!B27</f>
+        <f>'Cash Flow Statement'!B26</f>
         <v/>
       </c>
       <c r="C102" s="12">
-        <f>'Cash Flow Statement'!C27</f>
+        <f>'Cash Flow Statement'!C26</f>
         <v/>
       </c>
       <c r="D102" s="12">
-        <f>'Cash Flow Statement'!D27</f>
+        <f>'Cash Flow Statement'!D26</f>
         <v/>
       </c>
       <c r="E102" s="12">
-        <f>'Cash Flow Statement'!E27</f>
+        <f>'Cash Flow Statement'!E26</f>
+        <v/>
+      </c>
+      <c r="F102" s="12">
+        <f>'Cash Flow Statement'!F26</f>
         <v/>
       </c>
     </row>
@@ -8524,6 +9113,10 @@
         <f>'Cash Flow Statement'!E13</f>
         <v/>
       </c>
+      <c r="F103" s="12">
+        <f>'Cash Flow Statement'!F13</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
@@ -8547,6 +9140,10 @@
         <f>'Cash Flow Statement'!E7</f>
         <v/>
       </c>
+      <c r="F104" s="12">
+        <f>'Cash Flow Statement'!F7</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
@@ -8555,19 +9152,23 @@
         </is>
       </c>
       <c r="B105" s="12">
-        <f>'Cash Flow Statement'!B39</f>
+        <f>'Cash Flow Statement'!B38</f>
         <v/>
       </c>
       <c r="C105" s="12">
-        <f>'Cash Flow Statement'!C39</f>
+        <f>'Cash Flow Statement'!C38</f>
         <v/>
       </c>
       <c r="D105" s="12">
-        <f>'Cash Flow Statement'!D39</f>
+        <f>'Cash Flow Statement'!D38</f>
         <v/>
       </c>
       <c r="E105" s="12">
-        <f>'Cash Flow Statement'!E39</f>
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F105" s="12">
+        <f>'Cash Flow Statement'!F38</f>
         <v/>
       </c>
     </row>
@@ -8581,6 +9182,7 @@
       <c r="C106" s="15" t="n"/>
       <c r="D106" s="15" t="n"/>
       <c r="E106" s="15" t="n"/>
+      <c r="F106" s="15" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
@@ -8589,19 +9191,23 @@
         </is>
       </c>
       <c r="B107" s="12">
-        <f>'Cash Flow Statement'!B40</f>
+        <f>'Cash Flow Statement'!B39</f>
         <v/>
       </c>
       <c r="C107" s="12">
-        <f>'Cash Flow Statement'!C40</f>
+        <f>'Cash Flow Statement'!C39</f>
         <v/>
       </c>
       <c r="D107" s="12">
-        <f>'Cash Flow Statement'!D40</f>
+        <f>'Cash Flow Statement'!D39</f>
         <v/>
       </c>
       <c r="E107" s="12">
-        <f>'Cash Flow Statement'!E40</f>
+        <f>'Cash Flow Statement'!E39</f>
+        <v/>
+      </c>
+      <c r="F107" s="12">
+        <f>'Cash Flow Statement'!F39</f>
         <v/>
       </c>
     </row>
@@ -8615,6 +9221,7 @@
       <c r="C108" s="15" t="n"/>
       <c r="D108" s="15" t="n"/>
       <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
@@ -8623,19 +9230,23 @@
         </is>
       </c>
       <c r="B109" s="12">
-        <f>'Cash Flow Statement'!B37</f>
+        <f>'Cash Flow Statement'!B36</f>
         <v/>
       </c>
       <c r="C109" s="12">
-        <f>'Cash Flow Statement'!C37</f>
+        <f>'Cash Flow Statement'!C36</f>
         <v/>
       </c>
       <c r="D109" s="12">
-        <f>'Cash Flow Statement'!D37</f>
+        <f>'Cash Flow Statement'!D36</f>
         <v/>
       </c>
       <c r="E109" s="12">
-        <f>'Cash Flow Statement'!E37</f>
+        <f>'Cash Flow Statement'!E36</f>
+        <v/>
+      </c>
+      <c r="F109" s="12">
+        <f>'Cash Flow Statement'!F36</f>
         <v/>
       </c>
     </row>
@@ -8649,6 +9260,7 @@
       <c r="C110" s="15" t="n"/>
       <c r="D110" s="15" t="n"/>
       <c r="E110" s="15" t="n"/>
+      <c r="F110" s="15" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
@@ -8657,19 +9269,23 @@
         </is>
       </c>
       <c r="B111" s="12">
-        <f>'Cash Flow Statement'!B38</f>
+        <f>'Cash Flow Statement'!B37</f>
         <v/>
       </c>
       <c r="C111" s="12">
-        <f>'Cash Flow Statement'!C38</f>
+        <f>'Cash Flow Statement'!C37</f>
         <v/>
       </c>
       <c r="D111" s="12">
-        <f>'Cash Flow Statement'!D38</f>
+        <f>'Cash Flow Statement'!D37</f>
         <v/>
       </c>
       <c r="E111" s="12">
-        <f>'Cash Flow Statement'!E38</f>
+        <f>'Cash Flow Statement'!E37</f>
+        <v/>
+      </c>
+      <c r="F111" s="12">
+        <f>'Cash Flow Statement'!F37</f>
         <v/>
       </c>
     </row>
@@ -8683,6 +9299,7 @@
       <c r="C112" s="15" t="n"/>
       <c r="D112" s="15" t="n"/>
       <c r="E112" s="15" t="n"/>
+      <c r="F112" s="15" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="10" t="inlineStr">
@@ -8713,6 +9330,10 @@
         <f>'Income Statement'!E19</f>
         <v/>
       </c>
+      <c r="F115" s="12">
+        <f>'Income Statement'!F19</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="10" t="inlineStr">
@@ -8736,6 +9357,10 @@
         <f>'Income Statement'!E14</f>
         <v/>
       </c>
+      <c r="F116" s="12">
+        <f>'Income Statement'!F14</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
@@ -8757,6 +9382,10 @@
       </c>
       <c r="E117" s="12">
         <f>'Income Statement'!E16</f>
+        <v/>
+      </c>
+      <c r="F117" s="12">
+        <f>'Income Statement'!F16</f>
         <v/>
       </c>
     </row>
@@ -8770,6 +9399,7 @@
       <c r="C118" s="14" t="n"/>
       <c r="D118" s="14" t="n"/>
       <c r="E118" s="14" t="n"/>
+      <c r="F118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
@@ -8781,6 +9411,7 @@
       <c r="C119" s="14" t="n"/>
       <c r="D119" s="14" t="n"/>
       <c r="E119" s="14" t="n"/>
+      <c r="F119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="inlineStr">
@@ -8792,6 +9423,7 @@
       <c r="C120" s="14" t="n"/>
       <c r="D120" s="14" t="n"/>
       <c r="E120" s="14" t="n"/>
+      <c r="F120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
@@ -8802,6 +9434,7 @@
       <c r="C121" s="14" t="n"/>
       <c r="D121" s="14" t="n"/>
       <c r="E121" s="14" t="n"/>
+      <c r="F121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
@@ -8812,6 +9445,7 @@
       <c r="C122" s="14" t="n"/>
       <c r="D122" s="14" t="n"/>
       <c r="E122" s="14" t="n"/>
+      <c r="F122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
@@ -8822,6 +9456,7 @@
       <c r="C123" s="14" t="n"/>
       <c r="D123" s="14" t="n"/>
       <c r="E123" s="14" t="n"/>
+      <c r="F123" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
@@ -8852,6 +9487,10 @@
         <f>'Balance Sheet'!E9</f>
         <v/>
       </c>
+      <c r="F126" s="12">
+        <f>'Balance Sheet'!F9</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
@@ -8873,6 +9512,10 @@
       </c>
       <c r="E127" s="12">
         <f>'Income Statement'!E19</f>
+        <v/>
+      </c>
+      <c r="F127" s="12">
+        <f>'Income Statement'!F19</f>
         <v/>
       </c>
     </row>
@@ -8886,6 +9529,7 @@
       <c r="C128" s="14" t="n"/>
       <c r="D128" s="14" t="n"/>
       <c r="E128" s="14" t="n"/>
+      <c r="F128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
@@ -8896,6 +9540,7 @@
       <c r="C129" s="15" t="n"/>
       <c r="D129" s="15" t="n"/>
       <c r="E129" s="15" t="n"/>
+      <c r="F129" s="15" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
@@ -8906,6 +9551,7 @@
       <c r="C130" s="15" t="n"/>
       <c r="D130" s="15" t="n"/>
       <c r="E130" s="15" t="n"/>
+      <c r="F130" s="15" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
@@ -8916,6 +9562,7 @@
       <c r="C131" s="15" t="n"/>
       <c r="D131" s="15" t="n"/>
       <c r="E131" s="15" t="n"/>
+      <c r="F131" s="15" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="10" t="inlineStr">
@@ -8926,6 +9573,7 @@
       <c r="C132" s="15" t="n"/>
       <c r="D132" s="15" t="n"/>
       <c r="E132" s="15" t="n"/>
+      <c r="F132" s="15" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
@@ -8934,19 +9582,23 @@
         </is>
       </c>
       <c r="B133" s="12">
-        <f>'Cash Flow Statement'!B25</f>
+        <f>'Cash Flow Statement'!B24</f>
         <v/>
       </c>
       <c r="C133" s="12">
-        <f>'Cash Flow Statement'!C25</f>
+        <f>'Cash Flow Statement'!C24</f>
         <v/>
       </c>
       <c r="D133" s="12">
-        <f>'Cash Flow Statement'!D25</f>
+        <f>'Cash Flow Statement'!D24</f>
         <v/>
       </c>
       <c r="E133" s="12">
-        <f>'Cash Flow Statement'!E25</f>
+        <f>'Cash Flow Statement'!E24</f>
+        <v/>
+      </c>
+      <c r="F133" s="12">
+        <f>'Cash Flow Statement'!F24</f>
         <v/>
       </c>
     </row>
@@ -8959,6 +9611,7 @@
       <c r="C134" s="15" t="n"/>
       <c r="D134" s="15" t="n"/>
       <c r="E134" s="15" t="n"/>
+      <c r="F134" s="15" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
@@ -8969,6 +9622,7 @@
       <c r="C135" s="15" t="n"/>
       <c r="D135" s="15" t="n"/>
       <c r="E135" s="15" t="n"/>
+      <c r="F135" s="15" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
@@ -8997,6 +9651,10 @@
       </c>
       <c r="E138" s="12">
         <f>'Balance Sheet'!E22</f>
+        <v/>
+      </c>
+      <c r="F138" s="12">
+        <f>'Balance Sheet'!F22</f>
         <v/>
       </c>
     </row>
@@ -9009,6 +9667,7 @@
       <c r="C139" s="15" t="n"/>
       <c r="D139" s="15" t="n"/>
       <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="10" t="inlineStr">
@@ -9019,6 +9678,7 @@
       <c r="C140" s="14" t="n"/>
       <c r="D140" s="14" t="n"/>
       <c r="E140" s="14" t="n"/>
+      <c r="F140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
@@ -9029,6 +9689,7 @@
       <c r="C141" s="15" t="n"/>
       <c r="D141" s="15" t="n"/>
       <c r="E141" s="15" t="n"/>
+      <c r="F141" s="15" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="10" t="inlineStr">
@@ -9039,6 +9700,7 @@
       <c r="C142" s="14" t="n"/>
       <c r="D142" s="14" t="n"/>
       <c r="E142" s="14" t="n"/>
+      <c r="F142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
@@ -9060,6 +9722,10 @@
       </c>
       <c r="E143" s="12">
         <f>'Balance Sheet'!E23</f>
+        <v/>
+      </c>
+      <c r="F143" s="12">
+        <f>'Balance Sheet'!F23</f>
         <v/>
       </c>
     </row>
@@ -9072,6 +9738,7 @@
       <c r="C144" s="15" t="n"/>
       <c r="D144" s="15" t="n"/>
       <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
@@ -9082,6 +9749,7 @@
       <c r="C145" s="14" t="n"/>
       <c r="D145" s="14" t="n"/>
       <c r="E145" s="14" t="n"/>
+      <c r="F145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="10" t="inlineStr">
@@ -9092,6 +9760,7 @@
       <c r="C146" s="15" t="n"/>
       <c r="D146" s="15" t="n"/>
       <c r="E146" s="15" t="n"/>
+      <c r="F146" s="15" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
@@ -9102,6 +9771,7 @@
       <c r="C147" s="14" t="n"/>
       <c r="D147" s="14" t="n"/>
       <c r="E147" s="14" t="n"/>
+      <c r="F147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="10" t="inlineStr">
@@ -9123,6 +9793,10 @@
       </c>
       <c r="E148" s="12">
         <f>E138+E143</f>
+        <v/>
+      </c>
+      <c r="F148" s="12">
+        <f>F138+F143</f>
         <v/>
       </c>
     </row>
@@ -9135,6 +9809,7 @@
       <c r="C149" s="15" t="n"/>
       <c r="D149" s="15" t="n"/>
       <c r="E149" s="15" t="n"/>
+      <c r="F149" s="15" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="10" t="inlineStr">
@@ -9145,6 +9820,7 @@
       <c r="C150" s="14" t="n"/>
       <c r="D150" s="14" t="n"/>
       <c r="E150" s="14" t="n"/>
+      <c r="F150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="10" t="inlineStr">
@@ -9155,6 +9831,7 @@
       <c r="C151" s="15" t="n"/>
       <c r="D151" s="15" t="n"/>
       <c r="E151" s="15" t="n"/>
+      <c r="F151" s="15" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
@@ -9165,6 +9842,7 @@
       <c r="C152" s="14" t="n"/>
       <c r="D152" s="14" t="n"/>
       <c r="E152" s="14" t="n"/>
+      <c r="F152" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9421,7 +10099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9429,6 +10107,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9452,15 +10131,18 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C4" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="D4" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="E4" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="F4" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -9474,6 +10156,7 @@
       <c r="C5" s="15" t="n"/>
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -9495,6 +10178,10 @@
       </c>
       <c r="E6" s="12">
         <f>'Condensed Financials'!E35</f>
+        <v/>
+      </c>
+      <c r="F6" s="12">
+        <f>'Condensed Financials'!F35</f>
         <v/>
       </c>
     </row>
@@ -9508,6 +10195,7 @@
       <c r="C7" s="16" t="n"/>
       <c r="D7" s="16" t="n"/>
       <c r="E7" s="16" t="n"/>
+      <c r="F7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -9519,6 +10207,7 @@
       <c r="C8" s="15" t="n"/>
       <c r="D8" s="15" t="n"/>
       <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -9540,6 +10229,10 @@
       </c>
       <c r="E10" s="12">
         <f>'Balance Sheet'!E36</f>
+        <v/>
+      </c>
+      <c r="F10" s="12">
+        <f>'Balance Sheet'!F36</f>
         <v/>
       </c>
     </row>
@@ -9552,6 +10245,7 @@
       <c r="C11" s="15" t="n"/>
       <c r="D11" s="15" t="n"/>
       <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -9562,6 +10256,7 @@
       <c r="C12" s="14" t="n"/>
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -9584,6 +10279,7 @@
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -9599,6 +10295,7 @@
       <c r="C16" s="16" t="n"/>
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -9614,6 +10311,7 @@
       <c r="C17" s="15" t="n"/>
       <c r="D17" s="15" t="n"/>
       <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -9633,6 +10331,7 @@
       </c>
       <c r="D18" s="14" t="n"/>
       <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -9657,6 +10356,10 @@
         <f>IF(ABS(E17-((E6-D6)-E15))&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
+      <c r="F19" s="10">
+        <f>IF(ABS(F17-((F6-E6)-F15))&lt;0.01,"OK","CHECK")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -9672,19 +10375,23 @@
         </is>
       </c>
       <c r="B22" s="12">
-        <f>'Cash Flow Statement'!B35</f>
+        <f>'Cash Flow Statement'!B34</f>
         <v/>
       </c>
       <c r="C22" s="12">
-        <f>'Cash Flow Statement'!C35</f>
+        <f>'Cash Flow Statement'!C34</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>'Cash Flow Statement'!D35</f>
+        <f>'Cash Flow Statement'!D34</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>'Cash Flow Statement'!E35</f>
+        <f>'Cash Flow Statement'!E34</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>'Cash Flow Statement'!F34</f>
         <v/>
       </c>
     </row>
@@ -9698,6 +10405,7 @@
       <c r="C23" s="14" t="n"/>
       <c r="D23" s="14" t="n"/>
       <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -9709,6 +10417,7 @@
       <c r="C24" s="14" t="n"/>
       <c r="D24" s="14" t="n"/>
       <c r="E24" s="14" t="n"/>
+      <c r="F24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
@@ -9720,6 +10429,7 @@
       <c r="C25" s="15" t="n"/>
       <c r="D25" s="15" t="n"/>
       <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9732,7 +10442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9740,6 +10450,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9770,15 +10481,18 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
+        <v>44591</v>
+      </c>
+      <c r="C5" s="11" t="n">
         <v>44955</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="D5" s="11" t="n">
         <v>45319</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="E5" s="11" t="n">
         <v>45690</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="F5" s="11" t="n">
         <v>46054</v>
       </c>
     </row>
@@ -9804,6 +10518,10 @@
         <f>'Condensed Financials'!E34</f>
         <v/>
       </c>
+      <c r="F6" s="12">
+        <f>'Condensed Financials'!F34</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -9827,6 +10545,10 @@
         <f>'Condensed Financials'!E44</f>
         <v/>
       </c>
+      <c r="F7" s="12">
+        <f>'Condensed Financials'!F44</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -9850,6 +10572,10 @@
         <f>'Condensed Financials'!E45</f>
         <v/>
       </c>
+      <c r="F8" s="12">
+        <f>'Condensed Financials'!F45</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -9871,6 +10597,10 @@
       </c>
       <c r="E9" s="12">
         <f>'Condensed Financials'!E46</f>
+        <v/>
+      </c>
+      <c r="F9" s="12">
+        <f>'Condensed Financials'!F46</f>
         <v/>
       </c>
     </row>
@@ -9884,6 +10614,7 @@
       <c r="C11" s="14" t="n"/>
       <c r="D11" s="14" t="n"/>
       <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -9895,6 +10626,7 @@
       <c r="C12" s="14" t="n"/>
       <c r="D12" s="14" t="n"/>
       <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -9906,6 +10638,7 @@
       <c r="C13" s="14" t="n"/>
       <c r="D13" s="14" t="n"/>
       <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -9921,6 +10654,7 @@
       <c r="C14" s="15" t="n"/>
       <c r="D14" s="15" t="n"/>
       <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -9936,6 +10670,7 @@
       <c r="C15" s="15" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -9951,6 +10686,7 @@
       <c r="C16" s="14" t="n"/>
       <c r="D16" s="14" t="n"/>
       <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -9973,6 +10709,7 @@
       <c r="C19" s="15" t="n"/>
       <c r="D19" s="15" t="n"/>
       <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -9988,6 +10725,7 @@
       <c r="C20" s="15" t="n"/>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -10003,6 +10741,7 @@
       <c r="C21" s="15" t="n"/>
       <c r="D21" s="15" t="n"/>
       <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -10018,6 +10757,7 @@
       <c r="C22" s="14" t="n"/>
       <c r="D22" s="14" t="n"/>
       <c r="E22" s="14" t="n"/>
+      <c r="F22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -10033,6 +10773,7 @@
       <c r="C23" s="14" t="n"/>
       <c r="D23" s="14" t="n"/>
       <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -10055,6 +10796,10 @@
       </c>
       <c r="E24" s="10">
         <f>IF(ABS(E21-E15)&lt;0.01,"OK","CHECK")</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>IF(ABS(F21-F15)&lt;0.01,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
